--- a/inst/extdata/T1_rawdata.xlsx
+++ b/inst/extdata/T1_rawdata.xlsx
@@ -1,41 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tanac\Downloads\multi\raw\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tomoyoshi/Library/CloudStorage/GoogleDrive-tomoyoshi.kaneko@monash.edu/マイドライブ/literature/12_susiR/program/v7_順番指定機能/v7_3_revised_layout/inst/extdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B7DB7E4-1046-4B6D-B8E1-415103DAE992}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_8AC00CE11F8655E0F8CEB587149E0CB6504A2D4A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{490CF754-B2DD-4F35-B0A1-CA29B5D5C7B3}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="13120" windowHeight="14540" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="R" sheetId="2" r:id="rId1"/>
     <sheet name="name" sheetId="3" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="867" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="867" uniqueCount="587">
   <si>
     <t>A2</t>
   </si>
@@ -323,7 +314,7 @@
   </si>
   <si>
     <t>A1</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="0"/>
   </si>
   <si>
     <t>A13</t>
@@ -902,47 +893,909 @@
     <t>H36</t>
   </si>
   <si>
-    <t>num</t>
-    <phoneticPr fontId="1"/>
+    <t>Time</t>
+    <phoneticPr fontId="0"/>
+  </si>
+  <si>
+    <t>well</t>
   </si>
   <si>
     <t>sample</t>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Time</t>
-    <phoneticPr fontId="1"/>
+    <t>A1</t>
   </si>
   <si>
     <t>Ct</t>
   </si>
   <si>
+    <t>A2</t>
+  </si>
+  <si>
+    <t>A3</t>
+  </si>
+  <si>
+    <t>A4</t>
+  </si>
+  <si>
+    <t>A5</t>
+  </si>
+  <si>
+    <t>A6</t>
+  </si>
+  <si>
+    <t>A7</t>
+  </si>
+  <si>
+    <t>A8</t>
+  </si>
+  <si>
+    <t>A9</t>
+  </si>
+  <si>
+    <t>A10</t>
+  </si>
+  <si>
+    <t>A11</t>
+  </si>
+  <si>
+    <t>A12</t>
+  </si>
+  <si>
+    <t>B1</t>
+  </si>
+  <si>
     <t>free</t>
+  </si>
+  <si>
+    <t>B2</t>
+  </si>
+  <si>
+    <t>B3</t>
+  </si>
+  <si>
+    <t>B4</t>
+  </si>
+  <si>
+    <t>B5</t>
+  </si>
+  <si>
+    <t>B6</t>
+  </si>
+  <si>
+    <t>B7</t>
+  </si>
+  <si>
+    <t>B8</t>
+  </si>
+  <si>
+    <t>B9</t>
+  </si>
+  <si>
+    <t>B10</t>
+  </si>
+  <si>
+    <t>B11</t>
+  </si>
+  <si>
+    <t>B12</t>
+  </si>
+  <si>
+    <t>C1</t>
   </si>
   <si>
     <t>10^-5</t>
   </si>
   <si>
+    <t>C2</t>
+  </si>
+  <si>
+    <t>C3</t>
+  </si>
+  <si>
+    <t>C4</t>
+  </si>
+  <si>
+    <t>C5</t>
+  </si>
+  <si>
+    <t>C6</t>
+  </si>
+  <si>
+    <t>C7</t>
+  </si>
+  <si>
+    <t>C8</t>
+  </si>
+  <si>
+    <t>C9</t>
+  </si>
+  <si>
+    <t>C10</t>
+  </si>
+  <si>
+    <t>C11</t>
+  </si>
+  <si>
+    <t>C12</t>
+  </si>
+  <si>
+    <t>D1</t>
+  </si>
+  <si>
     <t>10^-4</t>
+  </si>
+  <si>
+    <t>D2</t>
+  </si>
+  <si>
+    <t>D3</t>
+  </si>
+  <si>
+    <t>D4</t>
+  </si>
+  <si>
+    <t>D5</t>
+  </si>
+  <si>
+    <t>D6</t>
+  </si>
+  <si>
+    <t>D7</t>
+  </si>
+  <si>
+    <t>D8</t>
+  </si>
+  <si>
+    <t>D9</t>
+  </si>
+  <si>
+    <t>D10</t>
+  </si>
+  <si>
+    <t>D11</t>
+  </si>
+  <si>
+    <t>D12</t>
+  </si>
+  <si>
+    <t>E1</t>
   </si>
   <si>
     <t>10^-3</t>
   </si>
   <si>
+    <t>E2</t>
+  </si>
+  <si>
+    <t>E3</t>
+  </si>
+  <si>
+    <t>E4</t>
+  </si>
+  <si>
+    <t>E5</t>
+  </si>
+  <si>
+    <t>E6</t>
+  </si>
+  <si>
+    <t>E7</t>
+  </si>
+  <si>
+    <t>E8</t>
+  </si>
+  <si>
+    <t>E9</t>
+  </si>
+  <si>
+    <t>E10</t>
+  </si>
+  <si>
+    <t>E11</t>
+  </si>
+  <si>
+    <t>E12</t>
+  </si>
+  <si>
+    <t>F1</t>
+  </si>
+  <si>
     <t>10^-2</t>
+  </si>
+  <si>
+    <t>F2</t>
+  </si>
+  <si>
+    <t>F3</t>
+  </si>
+  <si>
+    <t>F4</t>
+  </si>
+  <si>
+    <t>F5</t>
+  </si>
+  <si>
+    <t>F6</t>
+  </si>
+  <si>
+    <t>F7</t>
+  </si>
+  <si>
+    <t>F8</t>
+  </si>
+  <si>
+    <t>F9</t>
+  </si>
+  <si>
+    <t>F10</t>
+  </si>
+  <si>
+    <t>F11</t>
+  </si>
+  <si>
+    <t>F12</t>
+  </si>
+  <si>
+    <t>G1</t>
   </si>
   <si>
     <t>10^-1</t>
   </si>
   <si>
+    <t>G2</t>
+  </si>
+  <si>
+    <t>G3</t>
+  </si>
+  <si>
+    <t>G4</t>
+  </si>
+  <si>
+    <t>G5</t>
+  </si>
+  <si>
+    <t>G6</t>
+  </si>
+  <si>
+    <t>G7</t>
+  </si>
+  <si>
+    <t>G8</t>
+  </si>
+  <si>
+    <t>G9</t>
+  </si>
+  <si>
+    <t>G10</t>
+  </si>
+  <si>
+    <t>G11</t>
+  </si>
+  <si>
+    <t>G12</t>
+  </si>
+  <si>
+    <t>H1</t>
+  </si>
+  <si>
     <t>10^0</t>
+  </si>
+  <si>
+    <t>H2</t>
+  </si>
+  <si>
+    <t>H3</t>
+  </si>
+  <si>
+    <t>H4</t>
+  </si>
+  <si>
+    <t>H5</t>
+  </si>
+  <si>
+    <t>H6</t>
+  </si>
+  <si>
+    <t>H7</t>
+  </si>
+  <si>
+    <t>H8</t>
+  </si>
+  <si>
+    <t>H9</t>
+  </si>
+  <si>
+    <t>H10</t>
+  </si>
+  <si>
+    <t>H11</t>
+  </si>
+  <si>
+    <t>H12</t>
+  </si>
+  <si>
+    <t>A13</t>
+  </si>
+  <si>
+    <t>A14</t>
+  </si>
+  <si>
+    <t>A15</t>
+  </si>
+  <si>
+    <t>A16</t>
+  </si>
+  <si>
+    <t>A17</t>
+  </si>
+  <si>
+    <t>A18</t>
+  </si>
+  <si>
+    <t>A19</t>
+  </si>
+  <si>
+    <t>A20</t>
+  </si>
+  <si>
+    <t>A21</t>
+  </si>
+  <si>
+    <t>A22</t>
+  </si>
+  <si>
+    <t>A23</t>
+  </si>
+  <si>
+    <t>A24</t>
+  </si>
+  <si>
+    <t>B13</t>
+  </si>
+  <si>
+    <t>B14</t>
+  </si>
+  <si>
+    <t>B15</t>
+  </si>
+  <si>
+    <t>B16</t>
+  </si>
+  <si>
+    <t>B17</t>
+  </si>
+  <si>
+    <t>B18</t>
+  </si>
+  <si>
+    <t>B19</t>
+  </si>
+  <si>
+    <t>B20</t>
+  </si>
+  <si>
+    <t>B21</t>
+  </si>
+  <si>
+    <t>B22</t>
+  </si>
+  <si>
+    <t>B23</t>
+  </si>
+  <si>
+    <t>B24</t>
+  </si>
+  <si>
+    <t>C13</t>
+  </si>
+  <si>
+    <t>C14</t>
+  </si>
+  <si>
+    <t>C15</t>
+  </si>
+  <si>
+    <t>C16</t>
+  </si>
+  <si>
+    <t>C17</t>
+  </si>
+  <si>
+    <t>C18</t>
+  </si>
+  <si>
+    <t>C19</t>
+  </si>
+  <si>
+    <t>C20</t>
+  </si>
+  <si>
+    <t>C21</t>
+  </si>
+  <si>
+    <t>C22</t>
+  </si>
+  <si>
+    <t>C23</t>
+  </si>
+  <si>
+    <t>C24</t>
+  </si>
+  <si>
+    <t>D13</t>
+  </si>
+  <si>
+    <t>D14</t>
+  </si>
+  <si>
+    <t>D15</t>
+  </si>
+  <si>
+    <t>D16</t>
+  </si>
+  <si>
+    <t>D17</t>
+  </si>
+  <si>
+    <t>D18</t>
+  </si>
+  <si>
+    <t>D19</t>
+  </si>
+  <si>
+    <t>D20</t>
+  </si>
+  <si>
+    <t>D21</t>
+  </si>
+  <si>
+    <t>D22</t>
+  </si>
+  <si>
+    <t>D23</t>
+  </si>
+  <si>
+    <t>D24</t>
+  </si>
+  <si>
+    <t>E13</t>
+  </si>
+  <si>
+    <t>E14</t>
+  </si>
+  <si>
+    <t>E15</t>
+  </si>
+  <si>
+    <t>E16</t>
+  </si>
+  <si>
+    <t>E17</t>
+  </si>
+  <si>
+    <t>E18</t>
+  </si>
+  <si>
+    <t>E19</t>
+  </si>
+  <si>
+    <t>E20</t>
+  </si>
+  <si>
+    <t>E21</t>
+  </si>
+  <si>
+    <t>E22</t>
+  </si>
+  <si>
+    <t>E23</t>
+  </si>
+  <si>
+    <t>E24</t>
+  </si>
+  <si>
+    <t>F13</t>
+  </si>
+  <si>
+    <t>F14</t>
+  </si>
+  <si>
+    <t>F15</t>
+  </si>
+  <si>
+    <t>F16</t>
+  </si>
+  <si>
+    <t>F17</t>
+  </si>
+  <si>
+    <t>F18</t>
+  </si>
+  <si>
+    <t>F19</t>
+  </si>
+  <si>
+    <t>F20</t>
+  </si>
+  <si>
+    <t>F21</t>
+  </si>
+  <si>
+    <t>F22</t>
+  </si>
+  <si>
+    <t>F23</t>
+  </si>
+  <si>
+    <t>F24</t>
+  </si>
+  <si>
+    <t>G13</t>
+  </si>
+  <si>
+    <t>G14</t>
+  </si>
+  <si>
+    <t>G15</t>
+  </si>
+  <si>
+    <t>G16</t>
+  </si>
+  <si>
+    <t>G17</t>
+  </si>
+  <si>
+    <t>G18</t>
+  </si>
+  <si>
+    <t>G19</t>
+  </si>
+  <si>
+    <t>G20</t>
+  </si>
+  <si>
+    <t>G21</t>
+  </si>
+  <si>
+    <t>G22</t>
+  </si>
+  <si>
+    <t>G23</t>
+  </si>
+  <si>
+    <t>G24</t>
+  </si>
+  <si>
+    <t>H13</t>
+  </si>
+  <si>
+    <t>H14</t>
+  </si>
+  <si>
+    <t>H15</t>
+  </si>
+  <si>
+    <t>H16</t>
+  </si>
+  <si>
+    <t>H17</t>
+  </si>
+  <si>
+    <t>H18</t>
+  </si>
+  <si>
+    <t>H19</t>
+  </si>
+  <si>
+    <t>H20</t>
+  </si>
+  <si>
+    <t>H21</t>
+  </si>
+  <si>
+    <t>H22</t>
+  </si>
+  <si>
+    <t>H23</t>
+  </si>
+  <si>
+    <t>H24</t>
+  </si>
+  <si>
+    <t>A25</t>
+  </si>
+  <si>
+    <t>A26</t>
+  </si>
+  <si>
+    <t>A27</t>
+  </si>
+  <si>
+    <t>A28</t>
+  </si>
+  <si>
+    <t>A29</t>
+  </si>
+  <si>
+    <t>A30</t>
+  </si>
+  <si>
+    <t>A31</t>
+  </si>
+  <si>
+    <t>A32</t>
+  </si>
+  <si>
+    <t>A33</t>
+  </si>
+  <si>
+    <t>A34</t>
+  </si>
+  <si>
+    <t>A35</t>
+  </si>
+  <si>
+    <t>A36</t>
+  </si>
+  <si>
+    <t>B25</t>
+  </si>
+  <si>
+    <t>B26</t>
+  </si>
+  <si>
+    <t>B27</t>
+  </si>
+  <si>
+    <t>B28</t>
+  </si>
+  <si>
+    <t>B29</t>
+  </si>
+  <si>
+    <t>B30</t>
+  </si>
+  <si>
+    <t>B31</t>
+  </si>
+  <si>
+    <t>B32</t>
+  </si>
+  <si>
+    <t>B33</t>
+  </si>
+  <si>
+    <t>B34</t>
+  </si>
+  <si>
+    <t>B35</t>
+  </si>
+  <si>
+    <t>B36</t>
+  </si>
+  <si>
+    <t>C25</t>
+  </si>
+  <si>
+    <t>C26</t>
+  </si>
+  <si>
+    <t>C27</t>
+  </si>
+  <si>
+    <t>C28</t>
+  </si>
+  <si>
+    <t>C29</t>
+  </si>
+  <si>
+    <t>C30</t>
+  </si>
+  <si>
+    <t>C31</t>
+  </si>
+  <si>
+    <t>C32</t>
+  </si>
+  <si>
+    <t>C33</t>
+  </si>
+  <si>
+    <t>C34</t>
+  </si>
+  <si>
+    <t>C35</t>
+  </si>
+  <si>
+    <t>C36</t>
+  </si>
+  <si>
+    <t>D25</t>
+  </si>
+  <si>
+    <t>D26</t>
+  </si>
+  <si>
+    <t>D27</t>
+  </si>
+  <si>
+    <t>D28</t>
+  </si>
+  <si>
+    <t>D29</t>
+  </si>
+  <si>
+    <t>D30</t>
+  </si>
+  <si>
+    <t>D31</t>
+  </si>
+  <si>
+    <t>D32</t>
+  </si>
+  <si>
+    <t>D33</t>
+  </si>
+  <si>
+    <t>D34</t>
+  </si>
+  <si>
+    <t>D35</t>
+  </si>
+  <si>
+    <t>D36</t>
+  </si>
+  <si>
+    <t>E25</t>
+  </si>
+  <si>
+    <t>E26</t>
+  </si>
+  <si>
+    <t>E27</t>
+  </si>
+  <si>
+    <t>E28</t>
+  </si>
+  <si>
+    <t>E29</t>
+  </si>
+  <si>
+    <t>E30</t>
+  </si>
+  <si>
+    <t>E31</t>
+  </si>
+  <si>
+    <t>E32</t>
+  </si>
+  <si>
+    <t>E33</t>
+  </si>
+  <si>
+    <t>E34</t>
+  </si>
+  <si>
+    <t>E35</t>
+  </si>
+  <si>
+    <t>E36</t>
+  </si>
+  <si>
+    <t>F25</t>
+  </si>
+  <si>
+    <t>F26</t>
+  </si>
+  <si>
+    <t>F27</t>
+  </si>
+  <si>
+    <t>F28</t>
+  </si>
+  <si>
+    <t>F29</t>
+  </si>
+  <si>
+    <t>F30</t>
+  </si>
+  <si>
+    <t>F31</t>
+  </si>
+  <si>
+    <t>F32</t>
+  </si>
+  <si>
+    <t>F33</t>
+  </si>
+  <si>
+    <t>F34</t>
+  </si>
+  <si>
+    <t>F35</t>
+  </si>
+  <si>
+    <t>F36</t>
+  </si>
+  <si>
+    <t>G25</t>
+  </si>
+  <si>
+    <t>G26</t>
+  </si>
+  <si>
+    <t>G27</t>
+  </si>
+  <si>
+    <t>G28</t>
+  </si>
+  <si>
+    <t>G29</t>
+  </si>
+  <si>
+    <t>G30</t>
+  </si>
+  <si>
+    <t>G31</t>
+  </si>
+  <si>
+    <t>G32</t>
+  </si>
+  <si>
+    <t>G33</t>
+  </si>
+  <si>
+    <t>G34</t>
+  </si>
+  <si>
+    <t>G35</t>
+  </si>
+  <si>
+    <t>G36</t>
+  </si>
+  <si>
+    <t>H25</t>
+  </si>
+  <si>
+    <t>H26</t>
+  </si>
+  <si>
+    <t>H27</t>
+  </si>
+  <si>
+    <t>H28</t>
+  </si>
+  <si>
+    <t>H29</t>
+  </si>
+  <si>
+    <t>H30</t>
+  </si>
+  <si>
+    <t>H31</t>
+  </si>
+  <si>
+    <t>H32</t>
+  </si>
+  <si>
+    <t>H33</t>
+  </si>
+  <si>
+    <t>H34</t>
+  </si>
+  <si>
+    <t>H35</t>
+  </si>
+  <si>
+    <t>H36</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -977,14 +1830,10 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -1003,9 +1852,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1043,7 +1892,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1149,7 +1998,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1291,20 +2140,20 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83F04260-7336-420B-A0DF-06FA8794765D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:KC98"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <sheetData>
-    <row r="1" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:289">
       <c r="A1" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B1" t="s">
         <v>95</v>
@@ -2171,7 +3020,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="2" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:289">
       <c r="A2">
         <v>0</v>
       </c>
@@ -3040,7 +3889,7 @@
         <v>0.13900000000000001</v>
       </c>
     </row>
-    <row r="3" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:289">
       <c r="A3">
         <v>900</v>
       </c>
@@ -3909,7 +4758,7 @@
         <v>0.13900000000000001</v>
       </c>
     </row>
-    <row r="4" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:289">
       <c r="A4">
         <v>1800</v>
       </c>
@@ -4778,7 +5627,7 @@
         <v>0.157</v>
       </c>
     </row>
-    <row r="5" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:289">
       <c r="A5">
         <v>2700</v>
       </c>
@@ -5647,7 +6496,7 @@
         <v>0.158</v>
       </c>
     </row>
-    <row r="6" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:289">
       <c r="A6">
         <v>3600</v>
       </c>
@@ -6516,7 +7365,7 @@
         <v>9.1999999999999998E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:289">
       <c r="A7">
         <v>4500</v>
       </c>
@@ -7385,7 +8234,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="8" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:289">
       <c r="A8">
         <v>5400</v>
       </c>
@@ -8254,7 +9103,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="9" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:289">
       <c r="A9">
         <v>6300</v>
       </c>
@@ -9123,7 +9972,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="10" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:289">
       <c r="A10">
         <v>7200</v>
       </c>
@@ -9992,7 +10841,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="11" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:289">
       <c r="A11">
         <v>8100</v>
       </c>
@@ -10861,7 +11710,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="12" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:289">
       <c r="A12">
         <v>9000</v>
       </c>
@@ -11730,7 +12579,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="13" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:289">
       <c r="A13">
         <v>9900</v>
       </c>
@@ -12599,7 +13448,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="14" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:289">
       <c r="A14">
         <v>10800</v>
       </c>
@@ -13468,7 +14317,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="15" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:289">
       <c r="A15">
         <v>11700</v>
       </c>
@@ -14337,7 +15186,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="16" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:289">
       <c r="A16">
         <v>12600</v>
       </c>
@@ -15206,7 +16055,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="17" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:289">
       <c r="A17">
         <v>13500</v>
       </c>
@@ -16075,7 +16924,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="18" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:289">
       <c r="A18">
         <v>14400</v>
       </c>
@@ -16944,7 +17793,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="19" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:289">
       <c r="A19">
         <v>15300</v>
       </c>
@@ -17813,7 +18662,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="20" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:289">
       <c r="A20">
         <v>16200</v>
       </c>
@@ -18682,7 +19531,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="21" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:289">
       <c r="A21">
         <v>17100</v>
       </c>
@@ -19551,7 +20400,7 @@
         <v>9.0999999999999998E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:289">
       <c r="A22">
         <v>18000</v>
       </c>
@@ -20420,7 +21269,7 @@
         <v>9.0999999999999998E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:289">
       <c r="A23">
         <v>18900</v>
       </c>
@@ -21289,7 +22138,7 @@
         <v>9.0999999999999998E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:289">
       <c r="A24">
         <v>19800</v>
       </c>
@@ -22158,7 +23007,7 @@
         <v>9.1999999999999998E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:289">
       <c r="A25">
         <v>20700</v>
       </c>
@@ -23027,7 +23876,7 @@
         <v>9.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:289">
       <c r="A26">
         <v>21600</v>
       </c>
@@ -23896,7 +24745,7 @@
         <v>9.4E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:289">
       <c r="A27">
         <v>22500</v>
       </c>
@@ -24765,7 +25614,7 @@
         <v>9.7000000000000003E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:289">
       <c r="A28">
         <v>23400</v>
       </c>
@@ -25634,7 +26483,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="29" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:289">
       <c r="A29">
         <v>24300</v>
       </c>
@@ -26503,7 +27352,7 @@
         <v>0.107</v>
       </c>
     </row>
-    <row r="30" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:289">
       <c r="A30">
         <v>25200</v>
       </c>
@@ -27372,7 +28221,7 @@
         <v>0.11700000000000001</v>
       </c>
     </row>
-    <row r="31" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:289">
       <c r="A31">
         <v>26100</v>
       </c>
@@ -28241,7 +29090,7 @@
         <v>0.13500000000000001</v>
       </c>
     </row>
-    <row r="32" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:289">
       <c r="A32">
         <v>27000</v>
       </c>
@@ -29110,7 +29959,7 @@
         <v>0.16300000000000001</v>
       </c>
     </row>
-    <row r="33" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:289">
       <c r="A33">
         <v>27900</v>
       </c>
@@ -29979,7 +30828,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="34" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:289">
       <c r="A34">
         <v>28800</v>
       </c>
@@ -30848,7 +31697,7 @@
         <v>0.252</v>
       </c>
     </row>
-    <row r="35" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:289">
       <c r="A35">
         <v>29700</v>
       </c>
@@ -31717,7 +32566,7 @@
         <v>0.32100000000000001</v>
       </c>
     </row>
-    <row r="36" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:289">
       <c r="A36">
         <v>30600</v>
       </c>
@@ -32586,7 +33435,7 @@
         <v>0.39500000000000002</v>
       </c>
     </row>
-    <row r="37" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:289">
       <c r="A37">
         <v>31500</v>
       </c>
@@ -33455,7 +34304,7 @@
         <v>0.46200000000000002</v>
       </c>
     </row>
-    <row r="38" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:289">
       <c r="A38">
         <v>32400</v>
       </c>
@@ -34324,7 +35173,7 @@
         <v>0.53800000000000003</v>
       </c>
     </row>
-    <row r="39" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:289">
       <c r="A39">
         <v>33300</v>
       </c>
@@ -35193,7 +36042,7 @@
         <v>0.63100000000000001</v>
       </c>
     </row>
-    <row r="40" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:289">
       <c r="A40">
         <v>34200</v>
       </c>
@@ -36062,7 +36911,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="41" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:289">
       <c r="A41">
         <v>35100</v>
       </c>
@@ -36931,7 +37780,7 @@
         <v>0.76300000000000001</v>
       </c>
     </row>
-    <row r="42" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:289">
       <c r="A42">
         <v>36000</v>
       </c>
@@ -37800,7 +38649,7 @@
         <v>0.82699999999999996</v>
       </c>
     </row>
-    <row r="43" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:289">
       <c r="A43">
         <v>36900</v>
       </c>
@@ -38669,7 +39518,7 @@
         <v>0.89100000000000001</v>
       </c>
     </row>
-    <row r="44" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:289">
       <c r="A44">
         <v>37800</v>
       </c>
@@ -39538,7 +40387,7 @@
         <v>0.95199999999999996</v>
       </c>
     </row>
-    <row r="45" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:289">
       <c r="A45">
         <v>38700</v>
       </c>
@@ -40407,7 +41256,7 @@
         <v>1.006</v>
       </c>
     </row>
-    <row r="46" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:289">
       <c r="A46">
         <v>39600</v>
       </c>
@@ -41276,7 +42125,7 @@
         <v>1.0549999999999999</v>
       </c>
     </row>
-    <row r="47" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:289">
       <c r="A47">
         <v>40500</v>
       </c>
@@ -42145,7 +42994,7 @@
         <v>1.0880000000000001</v>
       </c>
     </row>
-    <row r="48" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:289">
       <c r="A48">
         <v>41400</v>
       </c>
@@ -43014,7 +43863,7 @@
         <v>1.115</v>
       </c>
     </row>
-    <row r="49" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:289">
       <c r="A49">
         <v>42300</v>
       </c>
@@ -43883,7 +44732,7 @@
         <v>1.1359999999999999</v>
       </c>
     </row>
-    <row r="50" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:289">
       <c r="A50">
         <v>43200</v>
       </c>
@@ -44752,7 +45601,7 @@
         <v>1.1539999999999999</v>
       </c>
     </row>
-    <row r="51" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:289">
       <c r="A51">
         <v>44100</v>
       </c>
@@ -45621,7 +46470,7 @@
         <v>1.17</v>
       </c>
     </row>
-    <row r="52" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:289">
       <c r="A52">
         <v>45000</v>
       </c>
@@ -46490,7 +47339,7 @@
         <v>1.1850000000000001</v>
       </c>
     </row>
-    <row r="53" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:289">
       <c r="A53">
         <v>45900</v>
       </c>
@@ -47359,7 +48208,7 @@
         <v>1.1990000000000001</v>
       </c>
     </row>
-    <row r="54" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:289">
       <c r="A54">
         <v>46800</v>
       </c>
@@ -48228,7 +49077,7 @@
         <v>1.212</v>
       </c>
     </row>
-    <row r="55" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:289">
       <c r="A55">
         <v>47700</v>
       </c>
@@ -49097,7 +49946,7 @@
         <v>1.224</v>
       </c>
     </row>
-    <row r="56" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:289">
       <c r="A56">
         <v>48600</v>
       </c>
@@ -49966,7 +50815,7 @@
         <v>1.236</v>
       </c>
     </row>
-    <row r="57" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:289">
       <c r="A57">
         <v>49500</v>
       </c>
@@ -50835,7 +51684,7 @@
         <v>1.2450000000000001</v>
       </c>
     </row>
-    <row r="58" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:289">
       <c r="A58">
         <v>50400</v>
       </c>
@@ -51704,7 +52553,7 @@
         <v>1.2549999999999999</v>
       </c>
     </row>
-    <row r="59" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:289">
       <c r="A59">
         <v>51300</v>
       </c>
@@ -52573,7 +53422,7 @@
         <v>1.262</v>
       </c>
     </row>
-    <row r="60" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:289">
       <c r="A60">
         <v>52200</v>
       </c>
@@ -53442,7 +54291,7 @@
         <v>1.2689999999999999</v>
       </c>
     </row>
-    <row r="61" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:289">
       <c r="A61">
         <v>53100</v>
       </c>
@@ -54311,7 +55160,7 @@
         <v>1.2749999999999999</v>
       </c>
     </row>
-    <row r="62" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:289">
       <c r="A62">
         <v>54000</v>
       </c>
@@ -55180,7 +56029,7 @@
         <v>1.28</v>
       </c>
     </row>
-    <row r="63" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:289">
       <c r="A63">
         <v>54900</v>
       </c>
@@ -56049,7 +56898,7 @@
         <v>1.284</v>
       </c>
     </row>
-    <row r="64" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="1:289">
       <c r="A64">
         <v>55800</v>
       </c>
@@ -56918,7 +57767,7 @@
         <v>1.2889999999999999</v>
       </c>
     </row>
-    <row r="65" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:289">
       <c r="A65">
         <v>56700</v>
       </c>
@@ -57787,7 +58636,7 @@
         <v>1.2929999999999999</v>
       </c>
     </row>
-    <row r="66" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:289">
       <c r="A66">
         <v>57600</v>
       </c>
@@ -58656,7 +59505,7 @@
         <v>1.2969999999999999</v>
       </c>
     </row>
-    <row r="67" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:289">
       <c r="A67">
         <v>58500</v>
       </c>
@@ -59525,7 +60374,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="68" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:289">
       <c r="A68">
         <v>59400</v>
       </c>
@@ -60394,7 +61243,7 @@
         <v>1.3049999999999999</v>
       </c>
     </row>
-    <row r="69" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:289">
       <c r="A69">
         <v>60300</v>
       </c>
@@ -61263,7 +62112,7 @@
         <v>1.31</v>
       </c>
     </row>
-    <row r="70" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:289">
       <c r="A70">
         <v>61200</v>
       </c>
@@ -62132,7 +62981,7 @@
         <v>1.3109999999999999</v>
       </c>
     </row>
-    <row r="71" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="1:289">
       <c r="A71">
         <v>62100</v>
       </c>
@@ -63001,7 +63850,7 @@
         <v>1.3129999999999999</v>
       </c>
     </row>
-    <row r="72" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="1:289">
       <c r="A72">
         <v>63000</v>
       </c>
@@ -63870,7 +64719,7 @@
         <v>1.3129999999999999</v>
       </c>
     </row>
-    <row r="73" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="1:289">
       <c r="A73">
         <v>63900</v>
       </c>
@@ -64739,7 +65588,7 @@
         <v>1.3129999999999999</v>
       </c>
     </row>
-    <row r="74" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="1:289">
       <c r="A74">
         <v>64800</v>
       </c>
@@ -65608,7 +66457,7 @@
         <v>1.3140000000000001</v>
       </c>
     </row>
-    <row r="75" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="1:289">
       <c r="A75">
         <v>65700</v>
       </c>
@@ -66477,7 +67326,7 @@
         <v>1.3129999999999999</v>
       </c>
     </row>
-    <row r="76" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="76" spans="1:289">
       <c r="A76">
         <v>66600</v>
       </c>
@@ -67346,7 +68195,7 @@
         <v>1.3120000000000001</v>
       </c>
     </row>
-    <row r="77" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="77" spans="1:289">
       <c r="A77">
         <v>67500</v>
       </c>
@@ -68215,7 +69064,7 @@
         <v>1.3129999999999999</v>
       </c>
     </row>
-    <row r="78" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="78" spans="1:289">
       <c r="A78">
         <v>68400</v>
       </c>
@@ -69084,7 +69933,7 @@
         <v>1.3120000000000001</v>
       </c>
     </row>
-    <row r="79" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="79" spans="1:289">
       <c r="A79">
         <v>69300</v>
       </c>
@@ -69953,7 +70802,7 @@
         <v>1.3109999999999999</v>
       </c>
     </row>
-    <row r="80" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="80" spans="1:289">
       <c r="A80">
         <v>70200</v>
       </c>
@@ -70822,7 +71671,7 @@
         <v>1.3120000000000001</v>
       </c>
     </row>
-    <row r="81" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="81" spans="1:289">
       <c r="A81">
         <v>71100</v>
       </c>
@@ -71691,7 +72540,7 @@
         <v>1.3109999999999999</v>
       </c>
     </row>
-    <row r="82" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="82" spans="1:289">
       <c r="A82">
         <v>72000</v>
       </c>
@@ -72560,7 +73409,7 @@
         <v>1.31</v>
       </c>
     </row>
-    <row r="83" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="83" spans="1:289">
       <c r="A83">
         <v>72900</v>
       </c>
@@ -73429,7 +74278,7 @@
         <v>1.31</v>
       </c>
     </row>
-    <row r="84" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="84" spans="1:289">
       <c r="A84">
         <v>73800</v>
       </c>
@@ -74298,7 +75147,7 @@
         <v>1.3089999999999999</v>
       </c>
     </row>
-    <row r="85" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="85" spans="1:289">
       <c r="A85">
         <v>74700</v>
       </c>
@@ -75167,7 +76016,7 @@
         <v>1.3080000000000001</v>
       </c>
     </row>
-    <row r="86" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="86" spans="1:289">
       <c r="A86">
         <v>75600</v>
       </c>
@@ -76036,7 +76885,7 @@
         <v>1.3080000000000001</v>
       </c>
     </row>
-    <row r="87" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="87" spans="1:289">
       <c r="A87">
         <v>76500</v>
       </c>
@@ -76905,7 +77754,7 @@
         <v>1.3080000000000001</v>
       </c>
     </row>
-    <row r="88" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="88" spans="1:289">
       <c r="A88">
         <v>77400</v>
       </c>
@@ -77774,7 +78623,7 @@
         <v>1.306</v>
       </c>
     </row>
-    <row r="89" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="89" spans="1:289">
       <c r="A89">
         <v>78300</v>
       </c>
@@ -78643,7 +79492,7 @@
         <v>1.306</v>
       </c>
     </row>
-    <row r="90" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="90" spans="1:289">
       <c r="A90">
         <v>79200</v>
       </c>
@@ -79512,7 +80361,7 @@
         <v>1.3049999999999999</v>
       </c>
     </row>
-    <row r="91" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="91" spans="1:289">
       <c r="A91">
         <v>80100</v>
       </c>
@@ -80381,7 +81230,7 @@
         <v>1.304</v>
       </c>
     </row>
-    <row r="92" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="92" spans="1:289">
       <c r="A92">
         <v>81000</v>
       </c>
@@ -81250,7 +82099,7 @@
         <v>1.3029999999999999</v>
       </c>
     </row>
-    <row r="93" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="93" spans="1:289">
       <c r="A93">
         <v>81900</v>
       </c>
@@ -82119,7 +82968,7 @@
         <v>1.302</v>
       </c>
     </row>
-    <row r="94" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="94" spans="1:289">
       <c r="A94">
         <v>82800</v>
       </c>
@@ -82988,7 +83837,7 @@
         <v>1.3009999999999999</v>
       </c>
     </row>
-    <row r="95" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="95" spans="1:289">
       <c r="A95">
         <v>83700</v>
       </c>
@@ -83857,7 +84706,7 @@
         <v>1.3009999999999999</v>
       </c>
     </row>
-    <row r="96" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="96" spans="1:289">
       <c r="A96">
         <v>84600</v>
       </c>
@@ -84726,7 +85575,7 @@
         <v>1.298</v>
       </c>
     </row>
-    <row r="97" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="97" spans="1:289">
       <c r="A97">
         <v>85500</v>
       </c>
@@ -85595,7 +86444,7 @@
         <v>1.298</v>
       </c>
     </row>
-    <row r="98" spans="1:289" x14ac:dyDescent="0.55000000000000004">
+    <row r="98" spans="1:289">
       <c r="A98">
         <v>86400</v>
       </c>
@@ -86467,2328 +87316,2330 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4D688FC-A73D-4852-95E7-7EFAD913CAF2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B289"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>95</v>
+        <v>291</v>
       </c>
       <c r="B2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>0</v>
+        <v>293</v>
       </c>
       <c r="B3" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>1</v>
+        <v>294</v>
       </c>
       <c r="B4" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>2</v>
+        <v>295</v>
       </c>
       <c r="B5" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>3</v>
+        <v>296</v>
       </c>
       <c r="B6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>4</v>
+        <v>297</v>
       </c>
       <c r="B7" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>5</v>
+        <v>298</v>
       </c>
       <c r="B8" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>6</v>
+        <v>299</v>
       </c>
       <c r="B9" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>7</v>
+        <v>300</v>
       </c>
       <c r="B10" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>8</v>
+        <v>301</v>
       </c>
       <c r="B11" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>9</v>
+        <v>302</v>
       </c>
       <c r="B12" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>10</v>
+        <v>303</v>
       </c>
       <c r="B13" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>11</v>
+        <v>304</v>
       </c>
       <c r="B14" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
+        <v>306</v>
+      </c>
+      <c r="B15" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
+        <v>307</v>
+      </c>
+      <c r="B16" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" t="s">
+        <v>308</v>
+      </c>
+      <c r="B17" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" t="s">
+        <v>309</v>
+      </c>
+      <c r="B18" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" t="s">
+        <v>310</v>
+      </c>
+      <c r="B19" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" t="s">
+        <v>311</v>
+      </c>
+      <c r="B20" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" t="s">
+        <v>312</v>
+      </c>
+      <c r="B21" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" t="s">
+        <v>313</v>
+      </c>
+      <c r="B22" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" t="s">
+        <v>314</v>
+      </c>
+      <c r="B23" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" t="s">
+        <v>315</v>
+      </c>
+      <c r="B24" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" t="s">
+        <v>316</v>
+      </c>
+      <c r="B25" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" t="s">
+        <v>317</v>
+      </c>
+      <c r="B26" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" t="s">
+        <v>319</v>
+      </c>
+      <c r="B27" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" t="s">
+        <v>320</v>
+      </c>
+      <c r="B28" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" t="s">
+        <v>321</v>
+      </c>
+      <c r="B29" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" t="s">
+        <v>322</v>
+      </c>
+      <c r="B30" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" t="s">
+        <v>323</v>
+      </c>
+      <c r="B31" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" t="s">
+        <v>324</v>
+      </c>
+      <c r="B32" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" t="s">
+        <v>325</v>
+      </c>
+      <c r="B33" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" t="s">
+        <v>326</v>
+      </c>
+      <c r="B34" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" t="s">
+        <v>327</v>
+      </c>
+      <c r="B35" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" t="s">
+        <v>328</v>
+      </c>
+      <c r="B36" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" t="s">
+        <v>329</v>
+      </c>
+      <c r="B37" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" t="s">
+        <v>330</v>
+      </c>
+      <c r="B38" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" t="s">
+        <v>332</v>
+      </c>
+      <c r="B39" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" t="s">
+        <v>333</v>
+      </c>
+      <c r="B40" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" t="s">
+        <v>334</v>
+      </c>
+      <c r="B41" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" t="s">
+        <v>335</v>
+      </c>
+      <c r="B42" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" t="s">
+        <v>336</v>
+      </c>
+      <c r="B43" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" t="s">
+        <v>337</v>
+      </c>
+      <c r="B44" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" t="s">
+        <v>338</v>
+      </c>
+      <c r="B45" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" t="s">
+        <v>339</v>
+      </c>
+      <c r="B46" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" t="s">
+        <v>340</v>
+      </c>
+      <c r="B47" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" t="s">
+        <v>341</v>
+      </c>
+      <c r="B48" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" t="s">
+        <v>342</v>
+      </c>
+      <c r="B49" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" t="s">
+        <v>343</v>
+      </c>
+      <c r="B50" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" t="s">
+        <v>345</v>
+      </c>
+      <c r="B51" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52" t="s">
+        <v>346</v>
+      </c>
+      <c r="B52" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" t="s">
+        <v>347</v>
+      </c>
+      <c r="B53" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" t="s">
+        <v>348</v>
+      </c>
+      <c r="B54" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55" t="s">
+        <v>349</v>
+      </c>
+      <c r="B55" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" t="s">
+        <v>350</v>
+      </c>
+      <c r="B56" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57" t="s">
+        <v>351</v>
+      </c>
+      <c r="B57" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58" t="s">
+        <v>352</v>
+      </c>
+      <c r="B58" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59" t="s">
+        <v>353</v>
+      </c>
+      <c r="B59" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60" t="s">
+        <v>354</v>
+      </c>
+      <c r="B60" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61" t="s">
+        <v>355</v>
+      </c>
+      <c r="B61" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62" t="s">
+        <v>356</v>
+      </c>
+      <c r="B62" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63" t="s">
+        <v>358</v>
+      </c>
+      <c r="B63" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64" t="s">
+        <v>359</v>
+      </c>
+      <c r="B64" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65" t="s">
+        <v>360</v>
+      </c>
+      <c r="B65" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66" t="s">
+        <v>361</v>
+      </c>
+      <c r="B66" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="A67" t="s">
+        <v>362</v>
+      </c>
+      <c r="B67" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68" t="s">
+        <v>363</v>
+      </c>
+      <c r="B68" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
+      <c r="A69" t="s">
+        <v>364</v>
+      </c>
+      <c r="B69" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="A70" t="s">
+        <v>365</v>
+      </c>
+      <c r="B70" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71" t="s">
+        <v>366</v>
+      </c>
+      <c r="B71" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72" t="s">
+        <v>367</v>
+      </c>
+      <c r="B72" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73" t="s">
+        <v>368</v>
+      </c>
+      <c r="B73" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74" t="s">
+        <v>369</v>
+      </c>
+      <c r="B74" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" t="s">
+        <v>371</v>
+      </c>
+      <c r="B75" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76" t="s">
+        <v>372</v>
+      </c>
+      <c r="B76" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" t="s">
+        <v>373</v>
+      </c>
+      <c r="B77" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78" t="s">
+        <v>374</v>
+      </c>
+      <c r="B78" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79" t="s">
+        <v>375</v>
+      </c>
+      <c r="B79" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80" t="s">
+        <v>376</v>
+      </c>
+      <c r="B80" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81" t="s">
+        <v>377</v>
+      </c>
+      <c r="B81" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82" t="s">
+        <v>378</v>
+      </c>
+      <c r="B82" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83" t="s">
+        <v>379</v>
+      </c>
+      <c r="B83" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
+      <c r="A84" t="s">
+        <v>380</v>
+      </c>
+      <c r="B84" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
+      <c r="A85" t="s">
+        <v>381</v>
+      </c>
+      <c r="B85" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
+      <c r="A86" t="s">
+        <v>382</v>
+      </c>
+      <c r="B86" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2">
+      <c r="A87" t="s">
+        <v>384</v>
+      </c>
+      <c r="B87" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2">
+      <c r="A88" t="s">
+        <v>385</v>
+      </c>
+      <c r="B88" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2">
+      <c r="A89" t="s">
+        <v>386</v>
+      </c>
+      <c r="B89" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2">
+      <c r="A90" t="s">
+        <v>387</v>
+      </c>
+      <c r="B90" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2">
+      <c r="A91" t="s">
+        <v>388</v>
+      </c>
+      <c r="B91" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2">
+      <c r="A92" t="s">
+        <v>389</v>
+      </c>
+      <c r="B92" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2">
+      <c r="A93" t="s">
+        <v>390</v>
+      </c>
+      <c r="B93" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2">
+      <c r="A94" t="s">
+        <v>391</v>
+      </c>
+      <c r="B94" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2">
+      <c r="A95" t="s">
+        <v>392</v>
+      </c>
+      <c r="B95" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2">
+      <c r="A96" t="s">
+        <v>393</v>
+      </c>
+      <c r="B96" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2">
+      <c r="A97" t="s">
+        <v>394</v>
+      </c>
+      <c r="B97" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2">
+      <c r="A98" t="s">
+        <v>395</v>
+      </c>
+      <c r="B98" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" t="s">
-        <v>12</v>
-      </c>
-      <c r="B15" t="s">
+    <row r="99" spans="1:2">
+      <c r="A99" t="s">
+        <v>396</v>
+      </c>
+      <c r="B99" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" t="s">
-        <v>13</v>
-      </c>
-      <c r="B16" t="s">
+    <row r="100" spans="1:2">
+      <c r="A100" t="s">
+        <v>397</v>
+      </c>
+      <c r="B100" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" t="s">
-        <v>14</v>
-      </c>
-      <c r="B17" t="s">
+    <row r="101" spans="1:2">
+      <c r="A101" t="s">
+        <v>398</v>
+      </c>
+      <c r="B101" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" t="s">
-        <v>15</v>
-      </c>
-      <c r="B18" t="s">
+    <row r="102" spans="1:2">
+      <c r="A102" t="s">
+        <v>399</v>
+      </c>
+      <c r="B102" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" t="s">
-        <v>16</v>
-      </c>
-      <c r="B19" t="s">
+    <row r="103" spans="1:2">
+      <c r="A103" t="s">
+        <v>400</v>
+      </c>
+      <c r="B103" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" t="s">
-        <v>17</v>
-      </c>
-      <c r="B20" t="s">
+    <row r="104" spans="1:2">
+      <c r="A104" t="s">
+        <v>401</v>
+      </c>
+      <c r="B104" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" t="s">
-        <v>18</v>
-      </c>
-      <c r="B21" t="s">
+    <row r="105" spans="1:2">
+      <c r="A105" t="s">
+        <v>402</v>
+      </c>
+      <c r="B105" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" t="s">
-        <v>19</v>
-      </c>
-      <c r="B22" t="s">
+    <row r="106" spans="1:2">
+      <c r="A106" t="s">
+        <v>403</v>
+      </c>
+      <c r="B106" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" t="s">
-        <v>20</v>
-      </c>
-      <c r="B23" t="s">
+    <row r="107" spans="1:2">
+      <c r="A107" t="s">
+        <v>404</v>
+      </c>
+      <c r="B107" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" t="s">
-        <v>21</v>
-      </c>
-      <c r="B24" t="s">
+    <row r="108" spans="1:2">
+      <c r="A108" t="s">
+        <v>405</v>
+      </c>
+      <c r="B108" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" t="s">
-        <v>22</v>
-      </c>
-      <c r="B25" t="s">
+    <row r="109" spans="1:2">
+      <c r="A109" t="s">
+        <v>406</v>
+      </c>
+      <c r="B109" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" t="s">
-        <v>23</v>
-      </c>
-      <c r="B26" t="s">
-        <v>293</v>
+    <row r="110" spans="1:2">
+      <c r="A110" t="s">
+        <v>407</v>
+      </c>
+      <c r="B110" t="s">
+        <v>305</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" t="s">
-        <v>24</v>
-      </c>
-      <c r="B27" t="s">
-        <v>293</v>
+    <row r="111" spans="1:2">
+      <c r="A111" t="s">
+        <v>408</v>
+      </c>
+      <c r="B111" t="s">
+        <v>305</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" t="s">
-        <v>25</v>
-      </c>
-      <c r="B28" t="s">
-        <v>293</v>
+    <row r="112" spans="1:2">
+      <c r="A112" t="s">
+        <v>409</v>
+      </c>
+      <c r="B112" t="s">
+        <v>305</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" t="s">
-        <v>26</v>
-      </c>
-      <c r="B29" t="s">
-        <v>293</v>
+    <row r="113" spans="1:2">
+      <c r="A113" t="s">
+        <v>410</v>
+      </c>
+      <c r="B113" t="s">
+        <v>305</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" t="s">
-        <v>27</v>
-      </c>
-      <c r="B30" t="s">
-        <v>293</v>
+    <row r="114" spans="1:2">
+      <c r="A114" t="s">
+        <v>411</v>
+      </c>
+      <c r="B114" t="s">
+        <v>305</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" t="s">
-        <v>28</v>
-      </c>
-      <c r="B31" t="s">
-        <v>293</v>
+    <row r="115" spans="1:2">
+      <c r="A115" t="s">
+        <v>412</v>
+      </c>
+      <c r="B115" t="s">
+        <v>305</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" t="s">
-        <v>29</v>
-      </c>
-      <c r="B32" t="s">
-        <v>293</v>
+    <row r="116" spans="1:2">
+      <c r="A116" t="s">
+        <v>413</v>
+      </c>
+      <c r="B116" t="s">
+        <v>305</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" t="s">
-        <v>30</v>
-      </c>
-      <c r="B33" t="s">
-        <v>293</v>
+    <row r="117" spans="1:2">
+      <c r="A117" t="s">
+        <v>414</v>
+      </c>
+      <c r="B117" t="s">
+        <v>305</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" t="s">
-        <v>31</v>
-      </c>
-      <c r="B34" t="s">
-        <v>293</v>
+    <row r="118" spans="1:2">
+      <c r="A118" t="s">
+        <v>415</v>
+      </c>
+      <c r="B118" t="s">
+        <v>305</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" t="s">
-        <v>32</v>
-      </c>
-      <c r="B35" t="s">
-        <v>293</v>
+    <row r="119" spans="1:2">
+      <c r="A119" t="s">
+        <v>416</v>
+      </c>
+      <c r="B119" t="s">
+        <v>305</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" t="s">
-        <v>33</v>
-      </c>
-      <c r="B36" t="s">
-        <v>293</v>
+    <row r="120" spans="1:2">
+      <c r="A120" t="s">
+        <v>417</v>
+      </c>
+      <c r="B120" t="s">
+        <v>305</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" t="s">
-        <v>34</v>
-      </c>
-      <c r="B37" t="s">
-        <v>293</v>
+    <row r="121" spans="1:2">
+      <c r="A121" t="s">
+        <v>418</v>
+      </c>
+      <c r="B121" t="s">
+        <v>305</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" t="s">
-        <v>35</v>
-      </c>
-      <c r="B38" t="s">
-        <v>294</v>
+    <row r="122" spans="1:2">
+      <c r="A122" t="s">
+        <v>419</v>
+      </c>
+      <c r="B122" t="s">
+        <v>318</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" t="s">
-        <v>36</v>
-      </c>
-      <c r="B39" t="s">
-        <v>294</v>
+    <row r="123" spans="1:2">
+      <c r="A123" t="s">
+        <v>420</v>
+      </c>
+      <c r="B123" t="s">
+        <v>318</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" t="s">
-        <v>37</v>
-      </c>
-      <c r="B40" t="s">
-        <v>294</v>
+    <row r="124" spans="1:2">
+      <c r="A124" t="s">
+        <v>421</v>
+      </c>
+      <c r="B124" t="s">
+        <v>318</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A41" t="s">
-        <v>38</v>
-      </c>
-      <c r="B41" t="s">
-        <v>294</v>
+    <row r="125" spans="1:2">
+      <c r="A125" t="s">
+        <v>422</v>
+      </c>
+      <c r="B125" t="s">
+        <v>318</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A42" t="s">
-        <v>39</v>
-      </c>
-      <c r="B42" t="s">
-        <v>294</v>
+    <row r="126" spans="1:2">
+      <c r="A126" t="s">
+        <v>423</v>
+      </c>
+      <c r="B126" t="s">
+        <v>318</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A43" t="s">
-        <v>40</v>
-      </c>
-      <c r="B43" t="s">
-        <v>294</v>
+    <row r="127" spans="1:2">
+      <c r="A127" t="s">
+        <v>424</v>
+      </c>
+      <c r="B127" t="s">
+        <v>318</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A44" t="s">
-        <v>41</v>
-      </c>
-      <c r="B44" t="s">
-        <v>294</v>
+    <row r="128" spans="1:2">
+      <c r="A128" t="s">
+        <v>425</v>
+      </c>
+      <c r="B128" t="s">
+        <v>318</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A45" t="s">
-        <v>42</v>
-      </c>
-      <c r="B45" t="s">
-        <v>294</v>
+    <row r="129" spans="1:2">
+      <c r="A129" t="s">
+        <v>426</v>
+      </c>
+      <c r="B129" t="s">
+        <v>318</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A46" t="s">
-        <v>43</v>
-      </c>
-      <c r="B46" t="s">
-        <v>294</v>
+    <row r="130" spans="1:2">
+      <c r="A130" t="s">
+        <v>427</v>
+      </c>
+      <c r="B130" t="s">
+        <v>318</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A47" t="s">
-        <v>44</v>
-      </c>
-      <c r="B47" t="s">
-        <v>294</v>
+    <row r="131" spans="1:2">
+      <c r="A131" t="s">
+        <v>428</v>
+      </c>
+      <c r="B131" t="s">
+        <v>318</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A48" t="s">
-        <v>45</v>
-      </c>
-      <c r="B48" t="s">
-        <v>294</v>
+    <row r="132" spans="1:2">
+      <c r="A132" t="s">
+        <v>429</v>
+      </c>
+      <c r="B132" t="s">
+        <v>318</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A49" t="s">
-        <v>46</v>
-      </c>
-      <c r="B49" t="s">
-        <v>294</v>
+    <row r="133" spans="1:2">
+      <c r="A133" t="s">
+        <v>430</v>
+      </c>
+      <c r="B133" t="s">
+        <v>318</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A50" t="s">
-        <v>47</v>
-      </c>
-      <c r="B50" t="s">
-        <v>295</v>
+    <row r="134" spans="1:2">
+      <c r="A134" t="s">
+        <v>431</v>
+      </c>
+      <c r="B134" t="s">
+        <v>331</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A51" t="s">
-        <v>48</v>
-      </c>
-      <c r="B51" t="s">
-        <v>295</v>
+    <row r="135" spans="1:2">
+      <c r="A135" t="s">
+        <v>432</v>
+      </c>
+      <c r="B135" t="s">
+        <v>331</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A52" t="s">
-        <v>49</v>
-      </c>
-      <c r="B52" t="s">
-        <v>295</v>
+    <row r="136" spans="1:2">
+      <c r="A136" t="s">
+        <v>433</v>
+      </c>
+      <c r="B136" t="s">
+        <v>331</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A53" t="s">
-        <v>50</v>
-      </c>
-      <c r="B53" t="s">
-        <v>295</v>
+    <row r="137" spans="1:2">
+      <c r="A137" t="s">
+        <v>434</v>
+      </c>
+      <c r="B137" t="s">
+        <v>331</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A54" t="s">
-        <v>51</v>
-      </c>
-      <c r="B54" t="s">
-        <v>295</v>
+    <row r="138" spans="1:2">
+      <c r="A138" t="s">
+        <v>435</v>
+      </c>
+      <c r="B138" t="s">
+        <v>331</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A55" t="s">
-        <v>52</v>
-      </c>
-      <c r="B55" t="s">
-        <v>295</v>
+    <row r="139" spans="1:2">
+      <c r="A139" t="s">
+        <v>436</v>
+      </c>
+      <c r="B139" t="s">
+        <v>331</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A56" t="s">
-        <v>53</v>
-      </c>
-      <c r="B56" t="s">
-        <v>295</v>
+    <row r="140" spans="1:2">
+      <c r="A140" t="s">
+        <v>437</v>
+      </c>
+      <c r="B140" t="s">
+        <v>331</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A57" t="s">
-        <v>54</v>
-      </c>
-      <c r="B57" t="s">
-        <v>295</v>
+    <row r="141" spans="1:2">
+      <c r="A141" t="s">
+        <v>438</v>
+      </c>
+      <c r="B141" t="s">
+        <v>331</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A58" t="s">
-        <v>55</v>
-      </c>
-      <c r="B58" t="s">
-        <v>295</v>
+    <row r="142" spans="1:2">
+      <c r="A142" t="s">
+        <v>439</v>
+      </c>
+      <c r="B142" t="s">
+        <v>331</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A59" t="s">
-        <v>56</v>
-      </c>
-      <c r="B59" t="s">
-        <v>295</v>
+    <row r="143" spans="1:2">
+      <c r="A143" t="s">
+        <v>440</v>
+      </c>
+      <c r="B143" t="s">
+        <v>331</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A60" t="s">
-        <v>57</v>
-      </c>
-      <c r="B60" t="s">
-        <v>295</v>
+    <row r="144" spans="1:2">
+      <c r="A144" t="s">
+        <v>441</v>
+      </c>
+      <c r="B144" t="s">
+        <v>331</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A61" t="s">
-        <v>58</v>
-      </c>
-      <c r="B61" t="s">
-        <v>295</v>
+    <row r="145" spans="1:2">
+      <c r="A145" t="s">
+        <v>442</v>
+      </c>
+      <c r="B145" t="s">
+        <v>331</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A62" t="s">
-        <v>59</v>
-      </c>
-      <c r="B62" t="s">
-        <v>296</v>
+    <row r="146" spans="1:2">
+      <c r="A146" t="s">
+        <v>443</v>
+      </c>
+      <c r="B146" t="s">
+        <v>344</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A63" t="s">
-        <v>60</v>
-      </c>
-      <c r="B63" t="s">
-        <v>296</v>
+    <row r="147" spans="1:2">
+      <c r="A147" t="s">
+        <v>444</v>
+      </c>
+      <c r="B147" t="s">
+        <v>344</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A64" t="s">
-        <v>61</v>
-      </c>
-      <c r="B64" t="s">
-        <v>296</v>
+    <row r="148" spans="1:2">
+      <c r="A148" t="s">
+        <v>445</v>
+      </c>
+      <c r="B148" t="s">
+        <v>344</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A65" t="s">
-        <v>62</v>
-      </c>
-      <c r="B65" t="s">
-        <v>296</v>
+    <row r="149" spans="1:2">
+      <c r="A149" t="s">
+        <v>446</v>
+      </c>
+      <c r="B149" t="s">
+        <v>344</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A66" t="s">
-        <v>63</v>
-      </c>
-      <c r="B66" t="s">
-        <v>296</v>
+    <row r="150" spans="1:2">
+      <c r="A150" t="s">
+        <v>447</v>
+      </c>
+      <c r="B150" t="s">
+        <v>344</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A67" t="s">
-        <v>64</v>
-      </c>
-      <c r="B67" t="s">
-        <v>296</v>
+    <row r="151" spans="1:2">
+      <c r="A151" t="s">
+        <v>448</v>
+      </c>
+      <c r="B151" t="s">
+        <v>344</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A68" t="s">
-        <v>65</v>
-      </c>
-      <c r="B68" t="s">
-        <v>296</v>
+    <row r="152" spans="1:2">
+      <c r="A152" t="s">
+        <v>449</v>
+      </c>
+      <c r="B152" t="s">
+        <v>344</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A69" t="s">
-        <v>66</v>
-      </c>
-      <c r="B69" t="s">
-        <v>296</v>
+    <row r="153" spans="1:2">
+      <c r="A153" t="s">
+        <v>450</v>
+      </c>
+      <c r="B153" t="s">
+        <v>344</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A70" t="s">
-        <v>67</v>
-      </c>
-      <c r="B70" t="s">
-        <v>296</v>
+    <row r="154" spans="1:2">
+      <c r="A154" t="s">
+        <v>451</v>
+      </c>
+      <c r="B154" t="s">
+        <v>344</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A71" t="s">
-        <v>68</v>
-      </c>
-      <c r="B71" t="s">
-        <v>296</v>
+    <row r="155" spans="1:2">
+      <c r="A155" t="s">
+        <v>452</v>
+      </c>
+      <c r="B155" t="s">
+        <v>344</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A72" t="s">
-        <v>69</v>
-      </c>
-      <c r="B72" t="s">
-        <v>296</v>
+    <row r="156" spans="1:2">
+      <c r="A156" t="s">
+        <v>453</v>
+      </c>
+      <c r="B156" t="s">
+        <v>344</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A73" t="s">
-        <v>70</v>
-      </c>
-      <c r="B73" t="s">
-        <v>296</v>
+    <row r="157" spans="1:2">
+      <c r="A157" t="s">
+        <v>454</v>
+      </c>
+      <c r="B157" t="s">
+        <v>344</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A74" t="s">
-        <v>71</v>
-      </c>
-      <c r="B74" t="s">
-        <v>297</v>
+    <row r="158" spans="1:2">
+      <c r="A158" t="s">
+        <v>455</v>
+      </c>
+      <c r="B158" t="s">
+        <v>357</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A75" t="s">
-        <v>72</v>
-      </c>
-      <c r="B75" t="s">
-        <v>297</v>
+    <row r="159" spans="1:2">
+      <c r="A159" t="s">
+        <v>456</v>
+      </c>
+      <c r="B159" t="s">
+        <v>357</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A76" t="s">
-        <v>73</v>
-      </c>
-      <c r="B76" t="s">
-        <v>297</v>
+    <row r="160" spans="1:2">
+      <c r="A160" t="s">
+        <v>457</v>
+      </c>
+      <c r="B160" t="s">
+        <v>357</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A77" t="s">
-        <v>74</v>
-      </c>
-      <c r="B77" t="s">
-        <v>297</v>
+    <row r="161" spans="1:2">
+      <c r="A161" t="s">
+        <v>458</v>
+      </c>
+      <c r="B161" t="s">
+        <v>357</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A78" t="s">
-        <v>75</v>
-      </c>
-      <c r="B78" t="s">
-        <v>297</v>
+    <row r="162" spans="1:2">
+      <c r="A162" t="s">
+        <v>459</v>
+      </c>
+      <c r="B162" t="s">
+        <v>357</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A79" t="s">
-        <v>76</v>
-      </c>
-      <c r="B79" t="s">
-        <v>297</v>
+    <row r="163" spans="1:2">
+      <c r="A163" t="s">
+        <v>460</v>
+      </c>
+      <c r="B163" t="s">
+        <v>357</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A80" t="s">
-        <v>77</v>
-      </c>
-      <c r="B80" t="s">
-        <v>297</v>
+    <row r="164" spans="1:2">
+      <c r="A164" t="s">
+        <v>461</v>
+      </c>
+      <c r="B164" t="s">
+        <v>357</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A81" t="s">
-        <v>78</v>
-      </c>
-      <c r="B81" t="s">
-        <v>297</v>
+    <row r="165" spans="1:2">
+      <c r="A165" t="s">
+        <v>462</v>
+      </c>
+      <c r="B165" t="s">
+        <v>357</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A82" t="s">
-        <v>79</v>
-      </c>
-      <c r="B82" t="s">
-        <v>297</v>
+    <row r="166" spans="1:2">
+      <c r="A166" t="s">
+        <v>463</v>
+      </c>
+      <c r="B166" t="s">
+        <v>357</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A83" t="s">
-        <v>80</v>
-      </c>
-      <c r="B83" t="s">
-        <v>297</v>
+    <row r="167" spans="1:2">
+      <c r="A167" t="s">
+        <v>464</v>
+      </c>
+      <c r="B167" t="s">
+        <v>357</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A84" t="s">
-        <v>81</v>
-      </c>
-      <c r="B84" t="s">
-        <v>297</v>
+    <row r="168" spans="1:2">
+      <c r="A168" t="s">
+        <v>465</v>
+      </c>
+      <c r="B168" t="s">
+        <v>357</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A85" t="s">
-        <v>82</v>
-      </c>
-      <c r="B85" t="s">
-        <v>297</v>
+    <row r="169" spans="1:2">
+      <c r="A169" t="s">
+        <v>466</v>
+      </c>
+      <c r="B169" t="s">
+        <v>357</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A86" t="s">
-        <v>83</v>
-      </c>
-      <c r="B86" t="s">
-        <v>298</v>
+    <row r="170" spans="1:2">
+      <c r="A170" t="s">
+        <v>467</v>
+      </c>
+      <c r="B170" t="s">
+        <v>370</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A87" t="s">
-        <v>84</v>
-      </c>
-      <c r="B87" t="s">
-        <v>298</v>
+    <row r="171" spans="1:2">
+      <c r="A171" t="s">
+        <v>468</v>
+      </c>
+      <c r="B171" t="s">
+        <v>370</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A88" t="s">
-        <v>85</v>
-      </c>
-      <c r="B88" t="s">
-        <v>298</v>
+    <row r="172" spans="1:2">
+      <c r="A172" t="s">
+        <v>469</v>
+      </c>
+      <c r="B172" t="s">
+        <v>370</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A89" t="s">
-        <v>86</v>
-      </c>
-      <c r="B89" t="s">
-        <v>298</v>
+    <row r="173" spans="1:2">
+      <c r="A173" t="s">
+        <v>470</v>
+      </c>
+      <c r="B173" t="s">
+        <v>370</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A90" t="s">
-        <v>87</v>
-      </c>
-      <c r="B90" t="s">
-        <v>298</v>
+    <row r="174" spans="1:2">
+      <c r="A174" t="s">
+        <v>471</v>
+      </c>
+      <c r="B174" t="s">
+        <v>370</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A91" t="s">
-        <v>88</v>
-      </c>
-      <c r="B91" t="s">
-        <v>298</v>
+    <row r="175" spans="1:2">
+      <c r="A175" t="s">
+        <v>472</v>
+      </c>
+      <c r="B175" t="s">
+        <v>370</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A92" t="s">
-        <v>89</v>
-      </c>
-      <c r="B92" t="s">
-        <v>298</v>
+    <row r="176" spans="1:2">
+      <c r="A176" t="s">
+        <v>473</v>
+      </c>
+      <c r="B176" t="s">
+        <v>370</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A93" t="s">
-        <v>90</v>
-      </c>
-      <c r="B93" t="s">
-        <v>298</v>
+    <row r="177" spans="1:2">
+      <c r="A177" t="s">
+        <v>474</v>
+      </c>
+      <c r="B177" t="s">
+        <v>370</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A94" t="s">
-        <v>91</v>
-      </c>
-      <c r="B94" t="s">
-        <v>298</v>
+    <row r="178" spans="1:2">
+      <c r="A178" t="s">
+        <v>475</v>
+      </c>
+      <c r="B178" t="s">
+        <v>370</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A95" t="s">
-        <v>92</v>
-      </c>
-      <c r="B95" t="s">
-        <v>298</v>
+    <row r="179" spans="1:2">
+      <c r="A179" t="s">
+        <v>476</v>
+      </c>
+      <c r="B179" t="s">
+        <v>370</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A96" t="s">
-        <v>93</v>
-      </c>
-      <c r="B96" t="s">
-        <v>298</v>
+    <row r="180" spans="1:2">
+      <c r="A180" t="s">
+        <v>477</v>
+      </c>
+      <c r="B180" t="s">
+        <v>370</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A97" t="s">
-        <v>94</v>
-      </c>
-      <c r="B97" t="s">
-        <v>298</v>
+    <row r="181" spans="1:2">
+      <c r="A181" t="s">
+        <v>478</v>
+      </c>
+      <c r="B181" t="s">
+        <v>370</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A98" t="s">
-        <v>96</v>
-      </c>
-      <c r="B98" t="s">
-        <v>291</v>
+    <row r="182" spans="1:2">
+      <c r="A182" t="s">
+        <v>479</v>
+      </c>
+      <c r="B182" t="s">
+        <v>383</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A99" t="s">
-        <v>97</v>
-      </c>
-      <c r="B99" t="s">
-        <v>291</v>
+    <row r="183" spans="1:2">
+      <c r="A183" t="s">
+        <v>480</v>
+      </c>
+      <c r="B183" t="s">
+        <v>383</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A100" t="s">
-        <v>98</v>
-      </c>
-      <c r="B100" t="s">
-        <v>291</v>
+    <row r="184" spans="1:2">
+      <c r="A184" t="s">
+        <v>481</v>
+      </c>
+      <c r="B184" t="s">
+        <v>383</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A101" t="s">
-        <v>99</v>
-      </c>
-      <c r="B101" t="s">
-        <v>291</v>
+    <row r="185" spans="1:2">
+      <c r="A185" t="s">
+        <v>482</v>
+      </c>
+      <c r="B185" t="s">
+        <v>383</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A102" t="s">
-        <v>100</v>
-      </c>
-      <c r="B102" t="s">
-        <v>291</v>
+    <row r="186" spans="1:2">
+      <c r="A186" t="s">
+        <v>483</v>
+      </c>
+      <c r="B186" t="s">
+        <v>383</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A103" t="s">
-        <v>101</v>
-      </c>
-      <c r="B103" t="s">
-        <v>291</v>
+    <row r="187" spans="1:2">
+      <c r="A187" t="s">
+        <v>484</v>
+      </c>
+      <c r="B187" t="s">
+        <v>383</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A104" t="s">
-        <v>102</v>
-      </c>
-      <c r="B104" t="s">
-        <v>291</v>
+    <row r="188" spans="1:2">
+      <c r="A188" t="s">
+        <v>485</v>
+      </c>
+      <c r="B188" t="s">
+        <v>383</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A105" t="s">
-        <v>103</v>
-      </c>
-      <c r="B105" t="s">
-        <v>291</v>
+    <row r="189" spans="1:2">
+      <c r="A189" t="s">
+        <v>486</v>
+      </c>
+      <c r="B189" t="s">
+        <v>383</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A106" t="s">
-        <v>104</v>
-      </c>
-      <c r="B106" t="s">
-        <v>291</v>
+    <row r="190" spans="1:2">
+      <c r="A190" t="s">
+        <v>487</v>
+      </c>
+      <c r="B190" t="s">
+        <v>383</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A107" t="s">
-        <v>105</v>
-      </c>
-      <c r="B107" t="s">
-        <v>291</v>
+    <row r="191" spans="1:2">
+      <c r="A191" t="s">
+        <v>488</v>
+      </c>
+      <c r="B191" t="s">
+        <v>383</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A108" t="s">
-        <v>106</v>
-      </c>
-      <c r="B108" t="s">
-        <v>291</v>
+    <row r="192" spans="1:2">
+      <c r="A192" t="s">
+        <v>489</v>
+      </c>
+      <c r="B192" t="s">
+        <v>383</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A109" t="s">
-        <v>107</v>
-      </c>
-      <c r="B109" t="s">
-        <v>291</v>
+    <row r="193" spans="1:2">
+      <c r="A193" t="s">
+        <v>490</v>
+      </c>
+      <c r="B193" t="s">
+        <v>383</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A110" t="s">
-        <v>108</v>
-      </c>
-      <c r="B110" t="s">
+    <row r="194" spans="1:2">
+      <c r="A194" t="s">
+        <v>491</v>
+      </c>
+      <c r="B194" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A111" t="s">
-        <v>109</v>
-      </c>
-      <c r="B111" t="s">
+    <row r="195" spans="1:2">
+      <c r="A195" t="s">
+        <v>492</v>
+      </c>
+      <c r="B195" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A112" t="s">
-        <v>110</v>
-      </c>
-      <c r="B112" t="s">
+    <row r="196" spans="1:2">
+      <c r="A196" t="s">
+        <v>493</v>
+      </c>
+      <c r="B196" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A113" t="s">
-        <v>111</v>
-      </c>
-      <c r="B113" t="s">
+    <row r="197" spans="1:2">
+      <c r="A197" t="s">
+        <v>494</v>
+      </c>
+      <c r="B197" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A114" t="s">
-        <v>112</v>
-      </c>
-      <c r="B114" t="s">
+    <row r="198" spans="1:2">
+      <c r="A198" t="s">
+        <v>495</v>
+      </c>
+      <c r="B198" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A115" t="s">
-        <v>113</v>
-      </c>
-      <c r="B115" t="s">
+    <row r="199" spans="1:2">
+      <c r="A199" t="s">
+        <v>496</v>
+      </c>
+      <c r="B199" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A116" t="s">
-        <v>114</v>
-      </c>
-      <c r="B116" t="s">
+    <row r="200" spans="1:2">
+      <c r="A200" t="s">
+        <v>497</v>
+      </c>
+      <c r="B200" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A117" t="s">
-        <v>115</v>
-      </c>
-      <c r="B117" t="s">
+    <row r="201" spans="1:2">
+      <c r="A201" t="s">
+        <v>498</v>
+      </c>
+      <c r="B201" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A118" t="s">
-        <v>116</v>
-      </c>
-      <c r="B118" t="s">
+    <row r="202" spans="1:2">
+      <c r="A202" t="s">
+        <v>499</v>
+      </c>
+      <c r="B202" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A119" t="s">
-        <v>117</v>
-      </c>
-      <c r="B119" t="s">
+    <row r="203" spans="1:2">
+      <c r="A203" t="s">
+        <v>500</v>
+      </c>
+      <c r="B203" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A120" t="s">
-        <v>118</v>
-      </c>
-      <c r="B120" t="s">
+    <row r="204" spans="1:2">
+      <c r="A204" t="s">
+        <v>501</v>
+      </c>
+      <c r="B204" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A121" t="s">
-        <v>119</v>
-      </c>
-      <c r="B121" t="s">
+    <row r="205" spans="1:2">
+      <c r="A205" t="s">
+        <v>502</v>
+      </c>
+      <c r="B205" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A122" t="s">
-        <v>120</v>
-      </c>
-      <c r="B122" t="s">
-        <v>293</v>
+    <row r="206" spans="1:2">
+      <c r="A206" t="s">
+        <v>503</v>
+      </c>
+      <c r="B206" t="s">
+        <v>305</v>
       </c>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A123" t="s">
-        <v>121</v>
-      </c>
-      <c r="B123" t="s">
-        <v>293</v>
+    <row r="207" spans="1:2">
+      <c r="A207" t="s">
+        <v>504</v>
+      </c>
+      <c r="B207" t="s">
+        <v>305</v>
       </c>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A124" t="s">
-        <v>122</v>
-      </c>
-      <c r="B124" t="s">
-        <v>293</v>
+    <row r="208" spans="1:2">
+      <c r="A208" t="s">
+        <v>505</v>
+      </c>
+      <c r="B208" t="s">
+        <v>305</v>
       </c>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A125" t="s">
-        <v>123</v>
-      </c>
-      <c r="B125" t="s">
-        <v>293</v>
+    <row r="209" spans="1:2">
+      <c r="A209" t="s">
+        <v>506</v>
+      </c>
+      <c r="B209" t="s">
+        <v>305</v>
       </c>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A126" t="s">
-        <v>124</v>
-      </c>
-      <c r="B126" t="s">
-        <v>293</v>
+    <row r="210" spans="1:2">
+      <c r="A210" t="s">
+        <v>507</v>
+      </c>
+      <c r="B210" t="s">
+        <v>305</v>
       </c>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A127" t="s">
-        <v>125</v>
-      </c>
-      <c r="B127" t="s">
-        <v>293</v>
+    <row r="211" spans="1:2">
+      <c r="A211" t="s">
+        <v>508</v>
+      </c>
+      <c r="B211" t="s">
+        <v>305</v>
       </c>
     </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A128" t="s">
-        <v>126</v>
-      </c>
-      <c r="B128" t="s">
-        <v>293</v>
+    <row r="212" spans="1:2">
+      <c r="A212" t="s">
+        <v>509</v>
+      </c>
+      <c r="B212" t="s">
+        <v>305</v>
       </c>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A129" t="s">
-        <v>127</v>
-      </c>
-      <c r="B129" t="s">
-        <v>293</v>
+    <row r="213" spans="1:2">
+      <c r="A213" t="s">
+        <v>510</v>
+      </c>
+      <c r="B213" t="s">
+        <v>305</v>
       </c>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A130" t="s">
-        <v>128</v>
-      </c>
-      <c r="B130" t="s">
-        <v>293</v>
+    <row r="214" spans="1:2">
+      <c r="A214" t="s">
+        <v>511</v>
+      </c>
+      <c r="B214" t="s">
+        <v>305</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A131" t="s">
-        <v>129</v>
-      </c>
-      <c r="B131" t="s">
-        <v>293</v>
+    <row r="215" spans="1:2">
+      <c r="A215" t="s">
+        <v>512</v>
+      </c>
+      <c r="B215" t="s">
+        <v>305</v>
       </c>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A132" t="s">
-        <v>130</v>
-      </c>
-      <c r="B132" t="s">
-        <v>293</v>
+    <row r="216" spans="1:2">
+      <c r="A216" t="s">
+        <v>513</v>
+      </c>
+      <c r="B216" t="s">
+        <v>305</v>
       </c>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A133" t="s">
-        <v>131</v>
-      </c>
-      <c r="B133" t="s">
-        <v>293</v>
+    <row r="217" spans="1:2">
+      <c r="A217" t="s">
+        <v>514</v>
+      </c>
+      <c r="B217" t="s">
+        <v>305</v>
       </c>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A134" t="s">
-        <v>132</v>
-      </c>
-      <c r="B134" t="s">
-        <v>294</v>
+    <row r="218" spans="1:2">
+      <c r="A218" t="s">
+        <v>515</v>
+      </c>
+      <c r="B218" t="s">
+        <v>318</v>
       </c>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A135" t="s">
-        <v>133</v>
-      </c>
-      <c r="B135" t="s">
-        <v>294</v>
+    <row r="219" spans="1:2">
+      <c r="A219" t="s">
+        <v>516</v>
+      </c>
+      <c r="B219" t="s">
+        <v>318</v>
       </c>
     </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A136" t="s">
-        <v>134</v>
-      </c>
-      <c r="B136" t="s">
-        <v>294</v>
+    <row r="220" spans="1:2">
+      <c r="A220" t="s">
+        <v>517</v>
+      </c>
+      <c r="B220" t="s">
+        <v>318</v>
       </c>
     </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A137" t="s">
-        <v>135</v>
-      </c>
-      <c r="B137" t="s">
-        <v>294</v>
+    <row r="221" spans="1:2">
+      <c r="A221" t="s">
+        <v>518</v>
+      </c>
+      <c r="B221" t="s">
+        <v>318</v>
       </c>
     </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A138" t="s">
-        <v>136</v>
-      </c>
-      <c r="B138" t="s">
-        <v>294</v>
+    <row r="222" spans="1:2">
+      <c r="A222" t="s">
+        <v>519</v>
+      </c>
+      <c r="B222" t="s">
+        <v>318</v>
       </c>
     </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A139" t="s">
-        <v>137</v>
-      </c>
-      <c r="B139" t="s">
-        <v>294</v>
+    <row r="223" spans="1:2">
+      <c r="A223" t="s">
+        <v>520</v>
+      </c>
+      <c r="B223" t="s">
+        <v>318</v>
       </c>
     </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A140" t="s">
-        <v>138</v>
-      </c>
-      <c r="B140" t="s">
-        <v>294</v>
+    <row r="224" spans="1:2">
+      <c r="A224" t="s">
+        <v>521</v>
+      </c>
+      <c r="B224" t="s">
+        <v>318</v>
       </c>
     </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A141" t="s">
-        <v>139</v>
-      </c>
-      <c r="B141" t="s">
-        <v>294</v>
+    <row r="225" spans="1:2">
+      <c r="A225" t="s">
+        <v>522</v>
+      </c>
+      <c r="B225" t="s">
+        <v>318</v>
       </c>
     </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A142" t="s">
-        <v>140</v>
-      </c>
-      <c r="B142" t="s">
-        <v>294</v>
+    <row r="226" spans="1:2">
+      <c r="A226" t="s">
+        <v>523</v>
+      </c>
+      <c r="B226" t="s">
+        <v>318</v>
       </c>
     </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A143" t="s">
-        <v>141</v>
-      </c>
-      <c r="B143" t="s">
-        <v>294</v>
+    <row r="227" spans="1:2">
+      <c r="A227" t="s">
+        <v>524</v>
+      </c>
+      <c r="B227" t="s">
+        <v>318</v>
       </c>
     </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A144" t="s">
-        <v>142</v>
-      </c>
-      <c r="B144" t="s">
-        <v>294</v>
+    <row r="228" spans="1:2">
+      <c r="A228" t="s">
+        <v>525</v>
+      </c>
+      <c r="B228" t="s">
+        <v>318</v>
       </c>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A145" t="s">
-        <v>143</v>
-      </c>
-      <c r="B145" t="s">
-        <v>294</v>
+    <row r="229" spans="1:2">
+      <c r="A229" t="s">
+        <v>526</v>
+      </c>
+      <c r="B229" t="s">
+        <v>318</v>
       </c>
     </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A146" t="s">
-        <v>144</v>
-      </c>
-      <c r="B146" t="s">
-        <v>295</v>
+    <row r="230" spans="1:2">
+      <c r="A230" t="s">
+        <v>527</v>
+      </c>
+      <c r="B230" t="s">
+        <v>331</v>
       </c>
     </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A147" t="s">
-        <v>145</v>
-      </c>
-      <c r="B147" t="s">
-        <v>295</v>
+    <row r="231" spans="1:2">
+      <c r="A231" t="s">
+        <v>528</v>
+      </c>
+      <c r="B231" t="s">
+        <v>331</v>
       </c>
     </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A148" t="s">
-        <v>146</v>
-      </c>
-      <c r="B148" t="s">
-        <v>295</v>
+    <row r="232" spans="1:2">
+      <c r="A232" t="s">
+        <v>529</v>
+      </c>
+      <c r="B232" t="s">
+        <v>331</v>
       </c>
     </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A149" t="s">
-        <v>147</v>
-      </c>
-      <c r="B149" t="s">
-        <v>295</v>
+    <row r="233" spans="1:2">
+      <c r="A233" t="s">
+        <v>530</v>
+      </c>
+      <c r="B233" t="s">
+        <v>331</v>
       </c>
     </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A150" t="s">
-        <v>148</v>
-      </c>
-      <c r="B150" t="s">
-        <v>295</v>
+    <row r="234" spans="1:2">
+      <c r="A234" t="s">
+        <v>531</v>
+      </c>
+      <c r="B234" t="s">
+        <v>331</v>
       </c>
     </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A151" t="s">
-        <v>149</v>
-      </c>
-      <c r="B151" t="s">
-        <v>295</v>
+    <row r="235" spans="1:2">
+      <c r="A235" t="s">
+        <v>532</v>
+      </c>
+      <c r="B235" t="s">
+        <v>331</v>
       </c>
     </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A152" t="s">
-        <v>150</v>
-      </c>
-      <c r="B152" t="s">
-        <v>295</v>
+    <row r="236" spans="1:2">
+      <c r="A236" t="s">
+        <v>533</v>
+      </c>
+      <c r="B236" t="s">
+        <v>331</v>
       </c>
     </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A153" t="s">
-        <v>151</v>
-      </c>
-      <c r="B153" t="s">
-        <v>295</v>
+    <row r="237" spans="1:2">
+      <c r="A237" t="s">
+        <v>534</v>
+      </c>
+      <c r="B237" t="s">
+        <v>331</v>
       </c>
     </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A154" t="s">
-        <v>152</v>
-      </c>
-      <c r="B154" t="s">
-        <v>295</v>
+    <row r="238" spans="1:2">
+      <c r="A238" t="s">
+        <v>535</v>
+      </c>
+      <c r="B238" t="s">
+        <v>331</v>
       </c>
     </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A155" t="s">
-        <v>153</v>
-      </c>
-      <c r="B155" t="s">
-        <v>295</v>
+    <row r="239" spans="1:2">
+      <c r="A239" t="s">
+        <v>536</v>
+      </c>
+      <c r="B239" t="s">
+        <v>331</v>
       </c>
     </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A156" t="s">
-        <v>154</v>
-      </c>
-      <c r="B156" t="s">
-        <v>295</v>
+    <row r="240" spans="1:2">
+      <c r="A240" t="s">
+        <v>537</v>
+      </c>
+      <c r="B240" t="s">
+        <v>331</v>
       </c>
     </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A157" t="s">
-        <v>155</v>
-      </c>
-      <c r="B157" t="s">
-        <v>295</v>
+    <row r="241" spans="1:2">
+      <c r="A241" t="s">
+        <v>538</v>
+      </c>
+      <c r="B241" t="s">
+        <v>331</v>
       </c>
     </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A158" t="s">
-        <v>156</v>
-      </c>
-      <c r="B158" t="s">
-        <v>296</v>
+    <row r="242" spans="1:2">
+      <c r="A242" t="s">
+        <v>539</v>
+      </c>
+      <c r="B242" t="s">
+        <v>344</v>
       </c>
     </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A159" t="s">
-        <v>157</v>
-      </c>
-      <c r="B159" t="s">
-        <v>296</v>
+    <row r="243" spans="1:2">
+      <c r="A243" t="s">
+        <v>540</v>
+      </c>
+      <c r="B243" t="s">
+        <v>344</v>
       </c>
     </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A160" t="s">
-        <v>158</v>
-      </c>
-      <c r="B160" t="s">
-        <v>296</v>
+    <row r="244" spans="1:2">
+      <c r="A244" t="s">
+        <v>541</v>
+      </c>
+      <c r="B244" t="s">
+        <v>344</v>
       </c>
     </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A161" t="s">
-        <v>159</v>
-      </c>
-      <c r="B161" t="s">
-        <v>296</v>
+    <row r="245" spans="1:2">
+      <c r="A245" t="s">
+        <v>542</v>
+      </c>
+      <c r="B245" t="s">
+        <v>344</v>
       </c>
     </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A162" t="s">
-        <v>160</v>
-      </c>
-      <c r="B162" t="s">
-        <v>296</v>
+    <row r="246" spans="1:2">
+      <c r="A246" t="s">
+        <v>543</v>
+      </c>
+      <c r="B246" t="s">
+        <v>344</v>
       </c>
     </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A163" t="s">
-        <v>161</v>
-      </c>
-      <c r="B163" t="s">
-        <v>296</v>
+    <row r="247" spans="1:2">
+      <c r="A247" t="s">
+        <v>544</v>
+      </c>
+      <c r="B247" t="s">
+        <v>344</v>
       </c>
     </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A164" t="s">
-        <v>162</v>
-      </c>
-      <c r="B164" t="s">
-        <v>296</v>
+    <row r="248" spans="1:2">
+      <c r="A248" t="s">
+        <v>545</v>
+      </c>
+      <c r="B248" t="s">
+        <v>344</v>
       </c>
     </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A165" t="s">
-        <v>163</v>
-      </c>
-      <c r="B165" t="s">
-        <v>296</v>
+    <row r="249" spans="1:2">
+      <c r="A249" t="s">
+        <v>546</v>
+      </c>
+      <c r="B249" t="s">
+        <v>344</v>
       </c>
     </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A166" t="s">
-        <v>164</v>
-      </c>
-      <c r="B166" t="s">
-        <v>296</v>
+    <row r="250" spans="1:2">
+      <c r="A250" t="s">
+        <v>547</v>
+      </c>
+      <c r="B250" t="s">
+        <v>344</v>
       </c>
     </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A167" t="s">
-        <v>165</v>
-      </c>
-      <c r="B167" t="s">
-        <v>296</v>
+    <row r="251" spans="1:2">
+      <c r="A251" t="s">
+        <v>548</v>
+      </c>
+      <c r="B251" t="s">
+        <v>344</v>
       </c>
     </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A168" t="s">
-        <v>166</v>
-      </c>
-      <c r="B168" t="s">
-        <v>296</v>
+    <row r="252" spans="1:2">
+      <c r="A252" t="s">
+        <v>549</v>
+      </c>
+      <c r="B252" t="s">
+        <v>344</v>
       </c>
     </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A169" t="s">
-        <v>167</v>
-      </c>
-      <c r="B169" t="s">
-        <v>296</v>
+    <row r="253" spans="1:2">
+      <c r="A253" t="s">
+        <v>550</v>
+      </c>
+      <c r="B253" t="s">
+        <v>344</v>
       </c>
     </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A170" t="s">
-        <v>168</v>
-      </c>
-      <c r="B170" t="s">
-        <v>297</v>
+    <row r="254" spans="1:2">
+      <c r="A254" t="s">
+        <v>551</v>
+      </c>
+      <c r="B254" t="s">
+        <v>357</v>
       </c>
     </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A171" t="s">
-        <v>169</v>
-      </c>
-      <c r="B171" t="s">
-        <v>297</v>
+    <row r="255" spans="1:2">
+      <c r="A255" t="s">
+        <v>552</v>
+      </c>
+      <c r="B255" t="s">
+        <v>357</v>
       </c>
     </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A172" t="s">
-        <v>170</v>
-      </c>
-      <c r="B172" t="s">
-        <v>297</v>
+    <row r="256" spans="1:2">
+      <c r="A256" t="s">
+        <v>553</v>
+      </c>
+      <c r="B256" t="s">
+        <v>357</v>
       </c>
     </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A173" t="s">
-        <v>171</v>
-      </c>
-      <c r="B173" t="s">
-        <v>297</v>
+    <row r="257" spans="1:2">
+      <c r="A257" t="s">
+        <v>554</v>
+      </c>
+      <c r="B257" t="s">
+        <v>357</v>
       </c>
     </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A174" t="s">
-        <v>172</v>
-      </c>
-      <c r="B174" t="s">
-        <v>297</v>
+    <row r="258" spans="1:2">
+      <c r="A258" t="s">
+        <v>555</v>
+      </c>
+      <c r="B258" t="s">
+        <v>357</v>
       </c>
     </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A175" t="s">
-        <v>173</v>
-      </c>
-      <c r="B175" t="s">
-        <v>297</v>
+    <row r="259" spans="1:2">
+      <c r="A259" t="s">
+        <v>556</v>
+      </c>
+      <c r="B259" t="s">
+        <v>357</v>
       </c>
     </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A176" t="s">
-        <v>174</v>
-      </c>
-      <c r="B176" t="s">
-        <v>297</v>
+    <row r="260" spans="1:2">
+      <c r="A260" t="s">
+        <v>557</v>
+      </c>
+      <c r="B260" t="s">
+        <v>357</v>
       </c>
     </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A177" t="s">
-        <v>175</v>
-      </c>
-      <c r="B177" t="s">
-        <v>297</v>
+    <row r="261" spans="1:2">
+      <c r="A261" t="s">
+        <v>558</v>
+      </c>
+      <c r="B261" t="s">
+        <v>357</v>
       </c>
     </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A178" t="s">
-        <v>176</v>
-      </c>
-      <c r="B178" t="s">
-        <v>297</v>
+    <row r="262" spans="1:2">
+      <c r="A262" t="s">
+        <v>559</v>
+      </c>
+      <c r="B262" t="s">
+        <v>357</v>
       </c>
     </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A179" t="s">
-        <v>177</v>
-      </c>
-      <c r="B179" t="s">
-        <v>297</v>
+    <row r="263" spans="1:2">
+      <c r="A263" t="s">
+        <v>560</v>
+      </c>
+      <c r="B263" t="s">
+        <v>357</v>
       </c>
     </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A180" t="s">
-        <v>178</v>
-      </c>
-      <c r="B180" t="s">
-        <v>297</v>
+    <row r="264" spans="1:2">
+      <c r="A264" t="s">
+        <v>561</v>
+      </c>
+      <c r="B264" t="s">
+        <v>357</v>
       </c>
     </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A181" t="s">
-        <v>179</v>
-      </c>
-      <c r="B181" t="s">
-        <v>297</v>
+    <row r="265" spans="1:2">
+      <c r="A265" t="s">
+        <v>562</v>
+      </c>
+      <c r="B265" t="s">
+        <v>357</v>
       </c>
     </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A182" t="s">
-        <v>180</v>
-      </c>
-      <c r="B182" t="s">
-        <v>298</v>
+    <row r="266" spans="1:2">
+      <c r="A266" t="s">
+        <v>563</v>
+      </c>
+      <c r="B266" t="s">
+        <v>370</v>
       </c>
     </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A183" t="s">
-        <v>181</v>
-      </c>
-      <c r="B183" t="s">
-        <v>298</v>
+    <row r="267" spans="1:2">
+      <c r="A267" t="s">
+        <v>564</v>
+      </c>
+      <c r="B267" t="s">
+        <v>370</v>
       </c>
     </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A184" t="s">
-        <v>182</v>
-      </c>
-      <c r="B184" t="s">
-        <v>298</v>
+    <row r="268" spans="1:2">
+      <c r="A268" t="s">
+        <v>565</v>
+      </c>
+      <c r="B268" t="s">
+        <v>370</v>
       </c>
     </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A185" t="s">
-        <v>183</v>
-      </c>
-      <c r="B185" t="s">
-        <v>298</v>
+    <row r="269" spans="1:2">
+      <c r="A269" t="s">
+        <v>566</v>
+      </c>
+      <c r="B269" t="s">
+        <v>370</v>
       </c>
     </row>
-    <row r="186" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A186" t="s">
-        <v>184</v>
-      </c>
-      <c r="B186" t="s">
-        <v>298</v>
+    <row r="270" spans="1:2">
+      <c r="A270" t="s">
+        <v>567</v>
+      </c>
+      <c r="B270" t="s">
+        <v>370</v>
       </c>
     </row>
-    <row r="187" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A187" t="s">
-        <v>185</v>
-      </c>
-      <c r="B187" t="s">
-        <v>298</v>
+    <row r="271" spans="1:2">
+      <c r="A271" t="s">
+        <v>568</v>
+      </c>
+      <c r="B271" t="s">
+        <v>370</v>
       </c>
     </row>
-    <row r="188" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A188" t="s">
-        <v>186</v>
-      </c>
-      <c r="B188" t="s">
-        <v>298</v>
+    <row r="272" spans="1:2">
+      <c r="A272" t="s">
+        <v>569</v>
+      </c>
+      <c r="B272" t="s">
+        <v>370</v>
       </c>
     </row>
-    <row r="189" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A189" t="s">
-        <v>187</v>
-      </c>
-      <c r="B189" t="s">
-        <v>298</v>
+    <row r="273" spans="1:2">
+      <c r="A273" t="s">
+        <v>570</v>
+      </c>
+      <c r="B273" t="s">
+        <v>370</v>
       </c>
     </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A190" t="s">
-        <v>188</v>
-      </c>
-      <c r="B190" t="s">
-        <v>298</v>
+    <row r="274" spans="1:2">
+      <c r="A274" t="s">
+        <v>571</v>
+      </c>
+      <c r="B274" t="s">
+        <v>370</v>
       </c>
     </row>
-    <row r="191" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A191" t="s">
-        <v>189</v>
-      </c>
-      <c r="B191" t="s">
-        <v>298</v>
+    <row r="275" spans="1:2">
+      <c r="A275" t="s">
+        <v>572</v>
+      </c>
+      <c r="B275" t="s">
+        <v>370</v>
       </c>
     </row>
-    <row r="192" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A192" t="s">
-        <v>190</v>
-      </c>
-      <c r="B192" t="s">
-        <v>298</v>
+    <row r="276" spans="1:2">
+      <c r="A276" t="s">
+        <v>573</v>
+      </c>
+      <c r="B276" t="s">
+        <v>370</v>
       </c>
     </row>
-    <row r="193" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A193" t="s">
-        <v>191</v>
-      </c>
-      <c r="B193" t="s">
-        <v>298</v>
+    <row r="277" spans="1:2">
+      <c r="A277" t="s">
+        <v>574</v>
+      </c>
+      <c r="B277" t="s">
+        <v>370</v>
       </c>
     </row>
-    <row r="194" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A194" t="s">
-        <v>192</v>
-      </c>
-      <c r="B194" t="s">
-        <v>291</v>
+    <row r="278" spans="1:2">
+      <c r="A278" t="s">
+        <v>575</v>
+      </c>
+      <c r="B278" t="s">
+        <v>383</v>
       </c>
     </row>
-    <row r="195" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A195" t="s">
-        <v>193</v>
-      </c>
-      <c r="B195" t="s">
-        <v>291</v>
+    <row r="279" spans="1:2">
+      <c r="A279" t="s">
+        <v>576</v>
+      </c>
+      <c r="B279" t="s">
+        <v>383</v>
       </c>
     </row>
-    <row r="196" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A196" t="s">
-        <v>194</v>
-      </c>
-      <c r="B196" t="s">
-        <v>291</v>
+    <row r="280" spans="1:2">
+      <c r="A280" t="s">
+        <v>577</v>
+      </c>
+      <c r="B280" t="s">
+        <v>383</v>
       </c>
     </row>
-    <row r="197" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A197" t="s">
-        <v>195</v>
-      </c>
-      <c r="B197" t="s">
-        <v>291</v>
+    <row r="281" spans="1:2">
+      <c r="A281" t="s">
+        <v>578</v>
+      </c>
+      <c r="B281" t="s">
+        <v>383</v>
       </c>
     </row>
-    <row r="198" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A198" t="s">
-        <v>196</v>
-      </c>
-      <c r="B198" t="s">
-        <v>291</v>
+    <row r="282" spans="1:2">
+      <c r="A282" t="s">
+        <v>579</v>
+      </c>
+      <c r="B282" t="s">
+        <v>383</v>
       </c>
     </row>
-    <row r="199" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A199" t="s">
-        <v>197</v>
-      </c>
-      <c r="B199" t="s">
-        <v>291</v>
+    <row r="283" spans="1:2">
+      <c r="A283" t="s">
+        <v>580</v>
+      </c>
+      <c r="B283" t="s">
+        <v>383</v>
       </c>
     </row>
-    <row r="200" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A200" t="s">
-        <v>198</v>
-      </c>
-      <c r="B200" t="s">
-        <v>291</v>
+    <row r="284" spans="1:2">
+      <c r="A284" t="s">
+        <v>581</v>
+      </c>
+      <c r="B284" t="s">
+        <v>383</v>
       </c>
     </row>
-    <row r="201" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A201" t="s">
-        <v>199</v>
-      </c>
-      <c r="B201" t="s">
-        <v>291</v>
+    <row r="285" spans="1:2">
+      <c r="A285" t="s">
+        <v>582</v>
+      </c>
+      <c r="B285" t="s">
+        <v>383</v>
       </c>
     </row>
-    <row r="202" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A202" t="s">
-        <v>200</v>
-      </c>
-      <c r="B202" t="s">
-        <v>291</v>
+    <row r="286" spans="1:2">
+      <c r="A286" t="s">
+        <v>583</v>
+      </c>
+      <c r="B286" t="s">
+        <v>383</v>
       </c>
     </row>
-    <row r="203" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A203" t="s">
-        <v>201</v>
-      </c>
-      <c r="B203" t="s">
-        <v>291</v>
+    <row r="287" spans="1:2">
+      <c r="A287" t="s">
+        <v>584</v>
+      </c>
+      <c r="B287" t="s">
+        <v>383</v>
       </c>
     </row>
-    <row r="204" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A204" t="s">
-        <v>202</v>
-      </c>
-      <c r="B204" t="s">
-        <v>291</v>
+    <row r="288" spans="1:2">
+      <c r="A288" t="s">
+        <v>585</v>
+      </c>
+      <c r="B288" t="s">
+        <v>383</v>
       </c>
     </row>
-    <row r="205" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A205" t="s">
-        <v>203</v>
-      </c>
-      <c r="B205" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="206" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A206" t="s">
-        <v>204</v>
-      </c>
-      <c r="B206" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="207" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A207" t="s">
-        <v>205</v>
-      </c>
-      <c r="B207" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="208" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A208" t="s">
-        <v>206</v>
-      </c>
-      <c r="B208" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="209" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A209" t="s">
-        <v>207</v>
-      </c>
-      <c r="B209" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="210" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A210" t="s">
-        <v>208</v>
-      </c>
-      <c r="B210" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="211" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A211" t="s">
-        <v>209</v>
-      </c>
-      <c r="B211" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="212" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A212" t="s">
-        <v>210</v>
-      </c>
-      <c r="B212" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="213" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A213" t="s">
-        <v>211</v>
-      </c>
-      <c r="B213" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="214" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A214" t="s">
-        <v>212</v>
-      </c>
-      <c r="B214" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="215" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A215" t="s">
-        <v>213</v>
-      </c>
-      <c r="B215" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="216" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A216" t="s">
-        <v>214</v>
-      </c>
-      <c r="B216" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="217" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A217" t="s">
-        <v>215</v>
-      </c>
-      <c r="B217" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="218" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A218" t="s">
-        <v>216</v>
-      </c>
-      <c r="B218" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="219" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A219" t="s">
-        <v>217</v>
-      </c>
-      <c r="B219" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="220" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A220" t="s">
-        <v>218</v>
-      </c>
-      <c r="B220" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="221" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A221" t="s">
-        <v>219</v>
-      </c>
-      <c r="B221" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="222" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A222" t="s">
-        <v>220</v>
-      </c>
-      <c r="B222" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="223" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A223" t="s">
-        <v>221</v>
-      </c>
-      <c r="B223" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="224" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A224" t="s">
-        <v>222</v>
-      </c>
-      <c r="B224" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="225" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A225" t="s">
-        <v>223</v>
-      </c>
-      <c r="B225" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="226" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A226" t="s">
-        <v>224</v>
-      </c>
-      <c r="B226" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="227" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A227" t="s">
-        <v>225</v>
-      </c>
-      <c r="B227" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="228" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A228" t="s">
-        <v>226</v>
-      </c>
-      <c r="B228" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="229" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A229" t="s">
-        <v>227</v>
-      </c>
-      <c r="B229" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="230" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A230" t="s">
-        <v>228</v>
-      </c>
-      <c r="B230" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="231" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A231" t="s">
-        <v>229</v>
-      </c>
-      <c r="B231" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="232" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A232" t="s">
-        <v>230</v>
-      </c>
-      <c r="B232" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="233" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A233" t="s">
-        <v>231</v>
-      </c>
-      <c r="B233" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="234" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A234" t="s">
-        <v>232</v>
-      </c>
-      <c r="B234" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="235" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A235" t="s">
-        <v>233</v>
-      </c>
-      <c r="B235" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="236" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A236" t="s">
-        <v>234</v>
-      </c>
-      <c r="B236" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="237" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A237" t="s">
-        <v>235</v>
-      </c>
-      <c r="B237" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="238" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A238" t="s">
-        <v>236</v>
-      </c>
-      <c r="B238" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="239" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A239" t="s">
-        <v>237</v>
-      </c>
-      <c r="B239" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="240" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A240" t="s">
-        <v>238</v>
-      </c>
-      <c r="B240" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="241" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A241" t="s">
-        <v>239</v>
-      </c>
-      <c r="B241" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="242" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A242" t="s">
-        <v>240</v>
-      </c>
-      <c r="B242" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="243" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A243" t="s">
-        <v>241</v>
-      </c>
-      <c r="B243" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="244" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A244" t="s">
-        <v>242</v>
-      </c>
-      <c r="B244" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="245" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A245" t="s">
-        <v>243</v>
-      </c>
-      <c r="B245" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="246" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A246" t="s">
-        <v>244</v>
-      </c>
-      <c r="B246" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="247" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A247" t="s">
-        <v>245</v>
-      </c>
-      <c r="B247" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="248" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A248" t="s">
-        <v>246</v>
-      </c>
-      <c r="B248" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="249" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A249" t="s">
-        <v>247</v>
-      </c>
-      <c r="B249" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="250" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A250" t="s">
-        <v>248</v>
-      </c>
-      <c r="B250" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="251" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A251" t="s">
-        <v>249</v>
-      </c>
-      <c r="B251" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="252" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A252" t="s">
-        <v>250</v>
-      </c>
-      <c r="B252" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="253" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A253" t="s">
-        <v>251</v>
-      </c>
-      <c r="B253" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="254" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A254" t="s">
-        <v>252</v>
-      </c>
-      <c r="B254" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="255" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A255" t="s">
-        <v>253</v>
-      </c>
-      <c r="B255" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="256" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A256" t="s">
-        <v>254</v>
-      </c>
-      <c r="B256" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="257" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A257" t="s">
-        <v>255</v>
-      </c>
-      <c r="B257" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="258" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A258" t="s">
-        <v>256</v>
-      </c>
-      <c r="B258" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="259" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A259" t="s">
-        <v>257</v>
-      </c>
-      <c r="B259" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="260" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A260" t="s">
-        <v>258</v>
-      </c>
-      <c r="B260" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="261" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A261" t="s">
-        <v>259</v>
-      </c>
-      <c r="B261" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="262" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A262" t="s">
-        <v>260</v>
-      </c>
-      <c r="B262" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="263" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A263" t="s">
-        <v>261</v>
-      </c>
-      <c r="B263" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="264" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A264" t="s">
-        <v>262</v>
-      </c>
-      <c r="B264" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="265" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A265" t="s">
-        <v>263</v>
-      </c>
-      <c r="B265" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="266" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A266" t="s">
-        <v>264</v>
-      </c>
-      <c r="B266" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="267" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A267" t="s">
-        <v>265</v>
-      </c>
-      <c r="B267" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="268" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A268" t="s">
-        <v>266</v>
-      </c>
-      <c r="B268" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="269" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A269" t="s">
-        <v>267</v>
-      </c>
-      <c r="B269" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="270" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A270" t="s">
-        <v>268</v>
-      </c>
-      <c r="B270" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="271" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A271" t="s">
-        <v>269</v>
-      </c>
-      <c r="B271" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="272" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A272" t="s">
-        <v>270</v>
-      </c>
-      <c r="B272" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="273" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A273" t="s">
-        <v>271</v>
-      </c>
-      <c r="B273" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="274" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A274" t="s">
-        <v>272</v>
-      </c>
-      <c r="B274" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="275" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A275" t="s">
-        <v>273</v>
-      </c>
-      <c r="B275" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="276" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A276" t="s">
-        <v>274</v>
-      </c>
-      <c r="B276" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="277" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A277" t="s">
-        <v>275</v>
-      </c>
-      <c r="B277" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="278" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A278" t="s">
-        <v>276</v>
-      </c>
-      <c r="B278" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="279" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A279" t="s">
-        <v>277</v>
-      </c>
-      <c r="B279" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="280" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A280" t="s">
-        <v>278</v>
-      </c>
-      <c r="B280" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="281" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A281" t="s">
-        <v>279</v>
-      </c>
-      <c r="B281" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="282" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A282" t="s">
-        <v>280</v>
-      </c>
-      <c r="B282" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="283" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A283" t="s">
-        <v>281</v>
-      </c>
-      <c r="B283" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="284" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A284" t="s">
-        <v>282</v>
-      </c>
-      <c r="B284" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="285" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A285" t="s">
-        <v>283</v>
-      </c>
-      <c r="B285" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="286" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A286" t="s">
-        <v>284</v>
-      </c>
-      <c r="B286" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="287" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A287" t="s">
-        <v>285</v>
-      </c>
-      <c r="B287" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="288" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A288" t="s">
-        <v>286</v>
-      </c>
-      <c r="B288" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="289" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="289" spans="1:2">
       <c r="A289" t="s">
-        <v>287</v>
+        <v>586</v>
       </c>
       <c r="B289" t="s">
-        <v>298</v>
+        <v>383</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>